--- a/files/Model2_RMS.xlsx
+++ b/files/Model2_RMS.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{597928CA-4F27-406B-A393-F47B97DB0755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90A8DFF-E456-4604-B807-4CCCE7590416}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{597928CA-4F27-406B-A393-F47B97DB0755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99B238D8-7E13-41A7-AB9C-A02471CB35E8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{143A15CA-C6F5-4023-A28E-AA4609974AFA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{143A15CA-C6F5-4023-A28E-AA4609974AFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Folha2" sheetId="2" r:id="rId2"/>
-    <sheet name="Folha3" sheetId="3" r:id="rId3"/>
+    <sheet name="Folha4" sheetId="4" r:id="rId2"/>
+    <sheet name="Folha2" sheetId="2" r:id="rId3"/>
+    <sheet name="Folha3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13920" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14703" uniqueCount="26">
   <si>
     <t>var</t>
   </si>
@@ -191,14 +192,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <strike val="0"/>
@@ -213,77 +207,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2052,6 +1975,7306 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6B1ABF-2891-4B72-9E9F-5BF65AFD97B8}">
+  <dimension ref="B3:BI42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>0.290502048517986</v>
+      </c>
+      <c r="C3">
+        <v>0.45612786946122202</v>
+      </c>
+      <c r="D3">
+        <v>0.626365655445004</v>
+      </c>
+      <c r="E3">
+        <v>0.73870044397747503</v>
+      </c>
+      <c r="F3">
+        <v>0.72710068608674505</v>
+      </c>
+      <c r="G3">
+        <v>0.77030300865866397</v>
+      </c>
+      <c r="H3">
+        <v>0.737709283379263</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>0.38415019953227098</v>
+      </c>
+      <c r="C4">
+        <v>0.27286276994954201</v>
+      </c>
+      <c r="D4">
+        <v>0.48673604804010601</v>
+      </c>
+      <c r="E4">
+        <v>0.4727722764342</v>
+      </c>
+      <c r="F4">
+        <v>0.66981310326334098</v>
+      </c>
+      <c r="G4">
+        <v>0.71909791447626203</v>
+      </c>
+      <c r="H4">
+        <v>0.55951544758652105</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" t="s">
+        <v>23</v>
+      </c>
+      <c r="X4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>0.177799295046142</v>
+      </c>
+      <c r="C5">
+        <v>0.35335881016624898</v>
+      </c>
+      <c r="D5">
+        <v>0.32645983025654701</v>
+      </c>
+      <c r="E5">
+        <v>0.33668124602052202</v>
+      </c>
+      <c r="F5">
+        <v>0.58814418050813799</v>
+      </c>
+      <c r="G5">
+        <v>0.73477486131763103</v>
+      </c>
+      <c r="H5">
+        <v>0.63269505957212602</v>
+      </c>
+      <c r="I5">
+        <v>0.484282308664157</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" t="s">
+        <v>23</v>
+      </c>
+      <c r="W5" t="s">
+        <v>23</v>
+      </c>
+      <c r="X5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>0.203453171324145</v>
+      </c>
+      <c r="C6">
+        <v>0.15459149367620201</v>
+      </c>
+      <c r="D6">
+        <v>0.21544130474779799</v>
+      </c>
+      <c r="E6">
+        <v>0.19659053236125301</v>
+      </c>
+      <c r="F6">
+        <v>0.44060354967370502</v>
+      </c>
+      <c r="G6">
+        <v>0.73097472522714302</v>
+      </c>
+      <c r="H6">
+        <v>0.68874992855211004</v>
+      </c>
+      <c r="I6">
+        <v>0.59394345874056298</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" t="s">
+        <v>23</v>
+      </c>
+      <c r="W6" t="s">
+        <v>23</v>
+      </c>
+      <c r="X6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>0.16979359922402901</v>
+      </c>
+      <c r="C7">
+        <v>9.7061779581474703E-2</v>
+      </c>
+      <c r="D7">
+        <v>0.22679398436902701</v>
+      </c>
+      <c r="E7">
+        <v>0.25763561291894199</v>
+      </c>
+      <c r="F7">
+        <v>0.26314577662574901</v>
+      </c>
+      <c r="G7">
+        <v>0.60531031896661802</v>
+      </c>
+      <c r="H7">
+        <v>0.72959122103784702</v>
+      </c>
+      <c r="I7">
+        <v>0.67229006876818698</v>
+      </c>
+      <c r="J7">
+        <v>0.60235647121872804</v>
+      </c>
+      <c r="K7">
+        <v>0.51907522332556699</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>23</v>
+      </c>
+      <c r="V7" t="s">
+        <v>23</v>
+      </c>
+      <c r="W7" t="s">
+        <v>23</v>
+      </c>
+      <c r="X7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>0.17485493785822501</v>
+      </c>
+      <c r="C8">
+        <v>9.7694893506273597E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.17112258037170899</v>
+      </c>
+      <c r="E8">
+        <v>0.113336463521254</v>
+      </c>
+      <c r="F8">
+        <v>0.154013281272081</v>
+      </c>
+      <c r="G8">
+        <v>0.21489508775566399</v>
+      </c>
+      <c r="H8">
+        <v>0.72739850233769399</v>
+      </c>
+      <c r="I8">
+        <v>0.72559159455268696</v>
+      </c>
+      <c r="J8">
+        <v>0.68229521042044095</v>
+      </c>
+      <c r="K8">
+        <v>0.63032646779784596</v>
+      </c>
+      <c r="L8">
+        <v>0.57801900433827202</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>23</v>
+      </c>
+      <c r="V8" t="s">
+        <v>23</v>
+      </c>
+      <c r="W8" t="s">
+        <v>23</v>
+      </c>
+      <c r="X8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>5.7144110505727402E-2</v>
+      </c>
+      <c r="C9">
+        <v>9.9178351602196901E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.106978633666823</v>
+      </c>
+      <c r="E9">
+        <v>9.7360704103995499E-2</v>
+      </c>
+      <c r="F9">
+        <v>0.139438280435076</v>
+      </c>
+      <c r="G9">
+        <v>0.12803796972629</v>
+      </c>
+      <c r="H9">
+        <v>0.54900721839226996</v>
+      </c>
+      <c r="I9">
+        <v>0.72922850135923101</v>
+      </c>
+      <c r="J9">
+        <v>0.72909137534169999</v>
+      </c>
+      <c r="K9">
+        <v>0.70161869674673105</v>
+      </c>
+      <c r="L9">
+        <v>0.66505195525455996</v>
+      </c>
+      <c r="M9">
+        <v>0.62662500362530504</v>
+      </c>
+      <c r="N9">
+        <v>0.58716566705059003</v>
+      </c>
+      <c r="O9">
+        <v>0.55006731704251599</v>
+      </c>
+      <c r="P9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>23</v>
+      </c>
+      <c r="V9" t="s">
+        <v>23</v>
+      </c>
+      <c r="W9" t="s">
+        <v>23</v>
+      </c>
+      <c r="X9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>0.208441766417333</v>
+      </c>
+      <c r="C10">
+        <v>0.10134806899868699</v>
+      </c>
+      <c r="D10">
+        <v>0.160298967470451</v>
+      </c>
+      <c r="E10">
+        <v>0.10215215275749499</v>
+      </c>
+      <c r="F10">
+        <v>0.12096020396389399</v>
+      </c>
+      <c r="G10">
+        <v>0.10991998258820999</v>
+      </c>
+      <c r="H10">
+        <v>0.13355869708180401</v>
+      </c>
+      <c r="I10">
+        <v>0.66711263814461697</v>
+      </c>
+      <c r="J10">
+        <v>0.73568118131057803</v>
+      </c>
+      <c r="K10">
+        <v>0.73681829345606598</v>
+      </c>
+      <c r="L10">
+        <v>0.71856123848972098</v>
+      </c>
+      <c r="M10">
+        <v>0.69235726436577805</v>
+      </c>
+      <c r="N10">
+        <v>0.66380034348274697</v>
+      </c>
+      <c r="O10">
+        <v>0.641245332336698</v>
+      </c>
+      <c r="P10">
+        <v>0.61332481352239099</v>
+      </c>
+      <c r="Q10">
+        <v>0.58487347543193402</v>
+      </c>
+      <c r="R10">
+        <v>0.55879123594413604</v>
+      </c>
+      <c r="S10" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>23</v>
+      </c>
+      <c r="V10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W10" t="s">
+        <v>23</v>
+      </c>
+      <c r="X10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>0.213561520768005</v>
+      </c>
+      <c r="C11">
+        <v>0.38466234221164097</v>
+      </c>
+      <c r="D11">
+        <v>6.9919993982511003E-2</v>
+      </c>
+      <c r="E11">
+        <v>0.10702191053289301</v>
+      </c>
+      <c r="F11">
+        <v>0.27343029649230299</v>
+      </c>
+      <c r="G11">
+        <v>0.15347705392834499</v>
+      </c>
+      <c r="H11">
+        <v>0.14963744723639499</v>
+      </c>
+      <c r="I11">
+        <v>0.10351716020158799</v>
+      </c>
+      <c r="J11">
+        <v>0.63547563950850805</v>
+      </c>
+      <c r="K11">
+        <v>0.71853098535276305</v>
+      </c>
+      <c r="L11">
+        <v>0.73703715238206002</v>
+      </c>
+      <c r="M11">
+        <v>0.73297444140156498</v>
+      </c>
+      <c r="N11">
+        <v>0.71992167548581198</v>
+      </c>
+      <c r="O11">
+        <v>0.70214777771810699</v>
+      </c>
+      <c r="P11">
+        <v>0.68190119645215397</v>
+      </c>
+      <c r="Q11">
+        <v>0.66581166296528904</v>
+      </c>
+      <c r="R11">
+        <v>0.64545530849899402</v>
+      </c>
+      <c r="S11">
+        <v>0.62498770010095495</v>
+      </c>
+      <c r="T11">
+        <v>0.60593785314343396</v>
+      </c>
+      <c r="U11">
+        <v>0.58733327831398996</v>
+      </c>
+      <c r="V11">
+        <v>0.56904749839312296</v>
+      </c>
+      <c r="W11" t="s">
+        <v>23</v>
+      </c>
+      <c r="X11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>6.7556378706197295E-2</v>
+      </c>
+      <c r="C12">
+        <v>0.148171406044599</v>
+      </c>
+      <c r="D12">
+        <v>6.5812705535889096E-2</v>
+      </c>
+      <c r="E12">
+        <v>0.10489205672292901</v>
+      </c>
+      <c r="F12">
+        <v>8.8360721176205498E-2</v>
+      </c>
+      <c r="G12">
+        <v>8.8971637502127804E-2</v>
+      </c>
+      <c r="H12">
+        <v>9.4419947313769695E-2</v>
+      </c>
+      <c r="I12">
+        <v>0.10023353989427</v>
+      </c>
+      <c r="J12">
+        <v>9.2787151212372507E-2</v>
+      </c>
+      <c r="K12">
+        <v>0.56297700668071105</v>
+      </c>
+      <c r="L12">
+        <v>0.67823656336881499</v>
+      </c>
+      <c r="M12">
+        <v>0.72049141286297003</v>
+      </c>
+      <c r="N12">
+        <v>0.73363291789769403</v>
+      </c>
+      <c r="O12">
+        <v>0.73308754626527495</v>
+      </c>
+      <c r="P12">
+        <v>0.72596867388042396</v>
+      </c>
+      <c r="Q12">
+        <v>0.71500559362335803</v>
+      </c>
+      <c r="R12">
+        <v>0.70228000961291404</v>
+      </c>
+      <c r="S12">
+        <v>0.69075201821437504</v>
+      </c>
+      <c r="T12">
+        <v>0.676835770604022</v>
+      </c>
+      <c r="U12">
+        <v>0.66290306974650903</v>
+      </c>
+      <c r="V12">
+        <v>0.64942755747313996</v>
+      </c>
+      <c r="W12">
+        <v>0.63587159633078505</v>
+      </c>
+      <c r="X12">
+        <v>0.62233268719971702</v>
+      </c>
+      <c r="Y12">
+        <v>0.60970544084512002</v>
+      </c>
+      <c r="Z12">
+        <v>0.60144439397657501</v>
+      </c>
+      <c r="AA12">
+        <v>0.58916089569840002</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>0.23900759001143099</v>
+      </c>
+      <c r="C13">
+        <v>0.15307320867640201</v>
+      </c>
+      <c r="D13">
+        <v>0.28434819577006798</v>
+      </c>
+      <c r="E13">
+        <v>7.2041156918514301E-2</v>
+      </c>
+      <c r="F13">
+        <v>7.8222474809943501E-2</v>
+      </c>
+      <c r="G13">
+        <v>0.119155045288939</v>
+      </c>
+      <c r="H13">
+        <v>0.12749437103169001</v>
+      </c>
+      <c r="I13">
+        <v>0.13621147917788101</v>
+      </c>
+      <c r="J13">
+        <v>0.148081143052153</v>
+      </c>
+      <c r="K13">
+        <v>0.15568928978991101</v>
+      </c>
+      <c r="L13">
+        <v>0.52645181722346401</v>
+      </c>
+      <c r="M13">
+        <v>0.64987474091999597</v>
+      </c>
+      <c r="N13">
+        <v>0.67375310383314402</v>
+      </c>
+      <c r="O13">
+        <v>0.710037858283874</v>
+      </c>
+      <c r="P13">
+        <v>0.72589908923243895</v>
+      </c>
+      <c r="Q13">
+        <v>0.73124318720173498</v>
+      </c>
+      <c r="R13">
+        <v>0.73056506012268196</v>
+      </c>
+      <c r="S13">
+        <v>0.72582128727099304</v>
+      </c>
+      <c r="T13">
+        <v>0.71905872357044998</v>
+      </c>
+      <c r="U13">
+        <v>0.71008143385896005</v>
+      </c>
+      <c r="V13">
+        <v>0.70210698888518996</v>
+      </c>
+      <c r="W13">
+        <v>0.69330929762896198</v>
+      </c>
+      <c r="X13">
+        <v>0.683961429990808</v>
+      </c>
+      <c r="Y13">
+        <v>0.67488039522069798</v>
+      </c>
+      <c r="Z13">
+        <v>0.665550910884672</v>
+      </c>
+      <c r="AA13">
+        <v>0.65794790835493999</v>
+      </c>
+      <c r="AB13">
+        <v>0.64874481011870999</v>
+      </c>
+      <c r="AC13">
+        <v>0.63950950963730402</v>
+      </c>
+      <c r="AD13">
+        <v>0.63087972601043996</v>
+      </c>
+      <c r="AE13">
+        <v>0.62361511791987601</v>
+      </c>
+      <c r="AF13">
+        <v>0.61527945226066905</v>
+      </c>
+      <c r="AG13">
+        <v>0.60686055608272504</v>
+      </c>
+      <c r="AH13">
+        <v>0.59860180656667505</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>9.3487121358343903E-2</v>
+      </c>
+      <c r="C14">
+        <v>0.177191518588665</v>
+      </c>
+      <c r="D14">
+        <v>0.10772408149034</v>
+      </c>
+      <c r="E14">
+        <v>0.14515893132425001</v>
+      </c>
+      <c r="F14">
+        <v>7.2126265118617597E-2</v>
+      </c>
+      <c r="G14">
+        <v>0.103716485137079</v>
+      </c>
+      <c r="H14">
+        <v>8.1514540190585794E-2</v>
+      </c>
+      <c r="I14">
+        <v>8.6647100453268802E-2</v>
+      </c>
+      <c r="J14">
+        <v>0.13549933536734099</v>
+      </c>
+      <c r="K14">
+        <v>0.14794179741141</v>
+      </c>
+      <c r="L14">
+        <v>9.3245090927477098E-2</v>
+      </c>
+      <c r="M14">
+        <v>0.34279999499564401</v>
+      </c>
+      <c r="N14">
+        <v>0.53363337379766895</v>
+      </c>
+      <c r="O14">
+        <v>0.62649376952388602</v>
+      </c>
+      <c r="P14">
+        <v>0.68060586904708198</v>
+      </c>
+      <c r="Q14">
+        <v>0.68492345492252105</v>
+      </c>
+      <c r="R14">
+        <v>0.708837901330027</v>
+      </c>
+      <c r="S14">
+        <v>0.720979989133542</v>
+      </c>
+      <c r="T14">
+        <v>0.72668936976603304</v>
+      </c>
+      <c r="U14">
+        <v>0.72872811597381104</v>
+      </c>
+      <c r="V14">
+        <v>0.72759401813464797</v>
+      </c>
+      <c r="W14">
+        <v>0.72027848917431703</v>
+      </c>
+      <c r="X14">
+        <v>0.71705262738174402</v>
+      </c>
+      <c r="Y14">
+        <v>0.71285559527336395</v>
+      </c>
+      <c r="Z14">
+        <v>0.70785093988286396</v>
+      </c>
+      <c r="AA14">
+        <v>0.70223080038484398</v>
+      </c>
+      <c r="AB14">
+        <v>0.69510056464340297</v>
+      </c>
+      <c r="AC14">
+        <v>0.68952607269348898</v>
+      </c>
+      <c r="AD14">
+        <v>0.68324194119756398</v>
+      </c>
+      <c r="AE14">
+        <v>0.67722886025285001</v>
+      </c>
+      <c r="AF14">
+        <v>0.67041477831346297</v>
+      </c>
+      <c r="AG14">
+        <v>0.66434533827169095</v>
+      </c>
+      <c r="AH14">
+        <v>0.65820603834182501</v>
+      </c>
+      <c r="AI14">
+        <v>0.65203256252556596</v>
+      </c>
+      <c r="AJ14">
+        <v>0.64591858700416305</v>
+      </c>
+      <c r="AK14">
+        <v>0.63978278333636796</v>
+      </c>
+      <c r="AL14">
+        <v>0.63421838878528602</v>
+      </c>
+      <c r="AM14">
+        <v>0.62820616666580398</v>
+      </c>
+      <c r="AN14">
+        <v>0.62259650511009901</v>
+      </c>
+      <c r="AO14">
+        <v>0.61677958063110006</v>
+      </c>
+      <c r="AP14">
+        <v>0.61128821607682204</v>
+      </c>
+      <c r="AQ14">
+        <v>0.60597593673255801</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>0.354981220459688</v>
+      </c>
+      <c r="C15">
+        <v>0.183090142713562</v>
+      </c>
+      <c r="D15">
+        <v>0.111729856602533</v>
+      </c>
+      <c r="E15">
+        <v>0.21684773333906501</v>
+      </c>
+      <c r="F15">
+        <v>6.4469469299832896E-2</v>
+      </c>
+      <c r="G15">
+        <v>6.9912916766888697E-2</v>
+      </c>
+      <c r="H15">
+        <v>7.7619374358919399E-2</v>
+      </c>
+      <c r="I15">
+        <v>0.123101648410527</v>
+      </c>
+      <c r="J15">
+        <v>0.127909637248969</v>
+      </c>
+      <c r="K15">
+        <v>0.134587731535556</v>
+      </c>
+      <c r="L15">
+        <v>0.14376415125720099</v>
+      </c>
+      <c r="M15">
+        <v>7.2115430955178597E-2</v>
+      </c>
+      <c r="N15">
+        <v>0.114674850847265</v>
+      </c>
+      <c r="O15">
+        <v>0.32500398863219698</v>
+      </c>
+      <c r="P15">
+        <v>0.47643749461787899</v>
+      </c>
+      <c r="Q15">
+        <v>0.57620704715746995</v>
+      </c>
+      <c r="R15">
+        <v>0.63762410409008696</v>
+      </c>
+      <c r="S15">
+        <v>0.67452244280585805</v>
+      </c>
+      <c r="T15">
+        <v>0.67437598942257104</v>
+      </c>
+      <c r="U15">
+        <v>0.69486476620431703</v>
+      </c>
+      <c r="V15">
+        <v>0.70940225089271203</v>
+      </c>
+      <c r="W15">
+        <v>0.71831516328399403</v>
+      </c>
+      <c r="X15">
+        <v>0.72319928488129204</v>
+      </c>
+      <c r="Y15">
+        <v>0.71647606119832197</v>
+      </c>
+      <c r="Z15">
+        <v>0.71880447686662896</v>
+      </c>
+      <c r="AA15">
+        <v>0.71915413219680102</v>
+      </c>
+      <c r="AB15">
+        <v>0.71853250318473005</v>
+      </c>
+      <c r="AC15">
+        <v>0.71159415973540097</v>
+      </c>
+      <c r="AD15">
+        <v>0.70982212953618995</v>
+      </c>
+      <c r="AE15">
+        <v>0.70742686488264195</v>
+      </c>
+      <c r="AF15">
+        <v>0.70102010690932703</v>
+      </c>
+      <c r="AG15">
+        <v>0.69783653655132805</v>
+      </c>
+      <c r="AH15">
+        <v>0.69453510428713605</v>
+      </c>
+      <c r="AI15">
+        <v>0.690891833946496</v>
+      </c>
+      <c r="AJ15">
+        <v>0.68507110096615298</v>
+      </c>
+      <c r="AK15">
+        <v>0.68125271615768102</v>
+      </c>
+      <c r="AL15">
+        <v>0.67724380504524595</v>
+      </c>
+      <c r="AM15">
+        <v>0.67134241564350905</v>
+      </c>
+      <c r="AN15">
+        <v>0.66755253558792405</v>
+      </c>
+      <c r="AO15">
+        <v>0.66179923449839895</v>
+      </c>
+      <c r="AP15">
+        <v>0.65795641477585798</v>
+      </c>
+      <c r="AQ15">
+        <v>0.65372614881701696</v>
+      </c>
+      <c r="AR15">
+        <v>0.64846918047410695</v>
+      </c>
+      <c r="AS15">
+        <v>0.64453451771100201</v>
+      </c>
+      <c r="AT15">
+        <v>0.63938843537333101</v>
+      </c>
+      <c r="AU15">
+        <v>0.63545585263945203</v>
+      </c>
+      <c r="AV15">
+        <v>0.63013853905074402</v>
+      </c>
+      <c r="AW15">
+        <v>0.62622846784903996</v>
+      </c>
+      <c r="AX15">
+        <v>0.621586716185759</v>
+      </c>
+      <c r="AY15">
+        <v>0.61770565409795297</v>
+      </c>
+      <c r="AZ15">
+        <v>0.61287920820577702</v>
+      </c>
+      <c r="BA15">
+        <v>0.60902317555483498</v>
+      </c>
+      <c r="BB15">
+        <v>0.60432016540999101</v>
+      </c>
+      <c r="BC15">
+        <v>0.59992018933682201</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>0.12830591835073801</v>
+      </c>
+      <c r="C16">
+        <v>8.5464170983877305E-2</v>
+      </c>
+      <c r="D16">
+        <v>0.137353964326832</v>
+      </c>
+      <c r="E16">
+        <v>8.4243827937503804E-2</v>
+      </c>
+      <c r="F16">
+        <v>0.10764445676172001</v>
+      </c>
+      <c r="G16">
+        <v>7.2514610905125398E-2</v>
+      </c>
+      <c r="H16">
+        <v>9.6918284587275E-2</v>
+      </c>
+      <c r="I16">
+        <v>9.8890361326235299E-2</v>
+      </c>
+      <c r="J16">
+        <v>0.123430393223721</v>
+      </c>
+      <c r="K16">
+        <v>0.12744126326340499</v>
+      </c>
+      <c r="L16">
+        <v>0.13313087850546801</v>
+      </c>
+      <c r="M16">
+        <v>0.14220720967311401</v>
+      </c>
+      <c r="N16">
+        <v>0.15165930646888701</v>
+      </c>
+      <c r="O16">
+        <v>5.8528956697931199E-2</v>
+      </c>
+      <c r="P16">
+        <v>0.21702643436447699</v>
+      </c>
+      <c r="Q16">
+        <v>0.25283806455436802</v>
+      </c>
+      <c r="R16">
+        <v>0.39505674083469</v>
+      </c>
+      <c r="S16">
+        <v>0.491849429008056</v>
+      </c>
+      <c r="T16">
+        <v>0.56438782079912597</v>
+      </c>
+      <c r="U16">
+        <v>0.61726745863982901</v>
+      </c>
+      <c r="V16">
+        <v>0.61183835299631195</v>
+      </c>
+      <c r="W16">
+        <v>0.64539559338593799</v>
+      </c>
+      <c r="X16">
+        <v>0.67064960818870401</v>
+      </c>
+      <c r="Y16">
+        <v>0.68769949672855801</v>
+      </c>
+      <c r="Z16">
+        <v>0.68062148556503299</v>
+      </c>
+      <c r="AA16">
+        <v>0.692821401565484</v>
+      </c>
+      <c r="AB16">
+        <v>0.70206930693008596</v>
+      </c>
+      <c r="AC16">
+        <v>0.70834874552973004</v>
+      </c>
+      <c r="AD16">
+        <v>0.70116158765376801</v>
+      </c>
+      <c r="AE16">
+        <v>0.70508761517155605</v>
+      </c>
+      <c r="AF16">
+        <v>0.70784888995530304</v>
+      </c>
+      <c r="AG16">
+        <v>0.708993683101381</v>
+      </c>
+      <c r="AH16">
+        <v>0.70261484587360801</v>
+      </c>
+      <c r="AI16">
+        <v>0.70304405187303498</v>
+      </c>
+      <c r="AJ16">
+        <v>0.70292633693917195</v>
+      </c>
+      <c r="AK16">
+        <v>0.69662748430751698</v>
+      </c>
+      <c r="AL16">
+        <v>0.69586706722892799</v>
+      </c>
+      <c r="AM16">
+        <v>0.68971784326084495</v>
+      </c>
+      <c r="AN16">
+        <v>0.68863786522453396</v>
+      </c>
+      <c r="AO16">
+        <v>0.68731421981391105</v>
+      </c>
+      <c r="AP16">
+        <v>0.68148914122650905</v>
+      </c>
+      <c r="AQ16">
+        <v>0.67966089995000101</v>
+      </c>
+      <c r="AR16">
+        <v>0.67408935773241097</v>
+      </c>
+      <c r="AS16">
+        <v>0.67229165786031597</v>
+      </c>
+      <c r="AT16">
+        <v>0.67025435631437402</v>
+      </c>
+      <c r="AU16">
+        <v>0.66483781692783495</v>
+      </c>
+      <c r="AV16">
+        <v>0.66252325418375801</v>
+      </c>
+      <c r="AW16">
+        <v>0.65731247172149199</v>
+      </c>
+      <c r="AX16">
+        <v>0.65503636187255199</v>
+      </c>
+      <c r="AY16">
+        <v>0.65011495497384997</v>
+      </c>
+      <c r="AZ16">
+        <v>0.64779003127055002</v>
+      </c>
+      <c r="BA16">
+        <v>0.64280338565045603</v>
+      </c>
+      <c r="BB16">
+        <v>0.63794522973324896</v>
+      </c>
+      <c r="BC16">
+        <v>0.63556210006189695</v>
+      </c>
+      <c r="BD16">
+        <v>0.63080878787178396</v>
+      </c>
+      <c r="BE16">
+        <v>0.62855843613004403</v>
+      </c>
+      <c r="BF16">
+        <v>0.62390192616951601</v>
+      </c>
+      <c r="BG16">
+        <v>0.62143810981323599</v>
+      </c>
+      <c r="BH16">
+        <v>0.61706947631076503</v>
+      </c>
+      <c r="BI16">
+        <v>0.61264580169804495</v>
+      </c>
+    </row>
+    <row r="17" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>0.13972686039533999</v>
+      </c>
+      <c r="C17">
+        <v>0.271836852020371</v>
+      </c>
+      <c r="D17">
+        <v>0.14358899386830501</v>
+      </c>
+      <c r="E17">
+        <v>0.31294742041120299</v>
+      </c>
+      <c r="F17">
+        <v>0.16710629783278499</v>
+      </c>
+      <c r="G17">
+        <v>8.23352976024945E-2</v>
+      </c>
+      <c r="H17">
+        <v>6.13765355772821E-2</v>
+      </c>
+      <c r="I17">
+        <v>6.3629164994574106E-2</v>
+      </c>
+      <c r="J17">
+        <v>7.1941647831406899E-2</v>
+      </c>
+      <c r="K17">
+        <v>0.219911179837396</v>
+      </c>
+      <c r="L17">
+        <v>0.12845393126628599</v>
+      </c>
+      <c r="M17">
+        <v>0.13337862655621499</v>
+      </c>
+      <c r="N17">
+        <v>0.13935392319120199</v>
+      </c>
+      <c r="O17">
+        <v>0.148276857031375</v>
+      </c>
+      <c r="P17">
+        <v>0.15550537418794899</v>
+      </c>
+      <c r="Q17">
+        <v>5.6938797215785798E-2</v>
+      </c>
+      <c r="R17">
+        <v>0.13974071204136501</v>
+      </c>
+      <c r="S17">
+        <v>0.155448153710496</v>
+      </c>
+      <c r="T17">
+        <v>0.26689891208090999</v>
+      </c>
+      <c r="U17">
+        <v>0.374380677622355</v>
+      </c>
+      <c r="V17">
+        <v>0.45777035418699402</v>
+      </c>
+      <c r="W17">
+        <v>0.52238035535508398</v>
+      </c>
+      <c r="X17">
+        <v>0.51288975362641598</v>
+      </c>
+      <c r="Y17">
+        <v>0.56312355533689895</v>
+      </c>
+      <c r="Z17">
+        <v>0.600976265576732</v>
+      </c>
+      <c r="AA17">
+        <v>0.62902027107957204</v>
+      </c>
+      <c r="AB17">
+        <v>0.61902567688378096</v>
+      </c>
+      <c r="AC17">
+        <v>0.64349934188935598</v>
+      </c>
+      <c r="AD17">
+        <v>0.65969978338247004</v>
+      </c>
+      <c r="AE17">
+        <v>0.67303406285460798</v>
+      </c>
+      <c r="AF17">
+        <v>0.66410941839356796</v>
+      </c>
+      <c r="AG17">
+        <v>0.67532280943290401</v>
+      </c>
+      <c r="AH17">
+        <v>0.68395635502561003</v>
+      </c>
+      <c r="AI17">
+        <v>0.67572081085732505</v>
+      </c>
+      <c r="AJ17">
+        <v>0.68198415104880405</v>
+      </c>
+      <c r="AK17">
+        <v>0.68712185648249702</v>
+      </c>
+      <c r="AL17">
+        <v>0.67978857709151097</v>
+      </c>
+      <c r="AM17">
+        <v>0.68367104798856504</v>
+      </c>
+      <c r="AN17">
+        <v>0.68703073280656801</v>
+      </c>
+      <c r="AO17">
+        <v>0.67992042958246901</v>
+      </c>
+      <c r="AP17">
+        <v>0.68240586775282597</v>
+      </c>
+      <c r="AQ17">
+        <v>0.67550795848977196</v>
+      </c>
+      <c r="AR17">
+        <v>0.67730801538639895</v>
+      </c>
+      <c r="AS17">
+        <v>0.67098038503050506</v>
+      </c>
+      <c r="AT17">
+        <v>0.67219559426855102</v>
+      </c>
+      <c r="AU17">
+        <v>0.67334752285657795</v>
+      </c>
+      <c r="AV17">
+        <v>0.6672145065067</v>
+      </c>
+      <c r="AW17">
+        <v>0.66750338594762204</v>
+      </c>
+      <c r="AX17">
+        <v>0.66152904127237</v>
+      </c>
+      <c r="AY17">
+        <v>0.66199082547258803</v>
+      </c>
+      <c r="AZ17">
+        <v>0.65629779949418499</v>
+      </c>
+      <c r="BA17">
+        <v>0.65619920269952003</v>
+      </c>
+      <c r="BB17">
+        <v>0.65074360063411796</v>
+      </c>
+      <c r="BC17">
+        <v>0.65050052023383098</v>
+      </c>
+      <c r="BD17">
+        <v>0.645166656130436</v>
+      </c>
+      <c r="BE17">
+        <v>0.64488409359895005</v>
+      </c>
+      <c r="BF17">
+        <v>0.63966891684289595</v>
+      </c>
+      <c r="BG17">
+        <v>0.63463549679071896</v>
+      </c>
+      <c r="BH17">
+        <v>0.63407389176103401</v>
+      </c>
+      <c r="BI17">
+        <v>0.62914496167042899</v>
+      </c>
+    </row>
+    <row r="18" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>0.15401955854836999</v>
+      </c>
+      <c r="C18">
+        <v>0.27855028056564601</v>
+      </c>
+      <c r="D18">
+        <v>0.21283954921002901</v>
+      </c>
+      <c r="E18">
+        <v>0.111101598638502</v>
+      </c>
+      <c r="F18">
+        <v>0.238847207407719</v>
+      </c>
+      <c r="G18">
+        <v>8.2374846003100494E-2</v>
+      </c>
+      <c r="H18">
+        <v>0.159311061489988</v>
+      </c>
+      <c r="I18">
+        <v>6.9261070929644203E-2</v>
+      </c>
+      <c r="J18">
+        <v>9.2865745749818304E-2</v>
+      </c>
+      <c r="K18">
+        <v>6.3603528134239001E-2</v>
+      </c>
+      <c r="L18">
+        <v>0.29119975555870797</v>
+      </c>
+      <c r="M18">
+        <v>0.12777095164399599</v>
+      </c>
+      <c r="N18">
+        <v>0.13132269504105701</v>
+      </c>
+      <c r="O18">
+        <v>0.13605435051724199</v>
+      </c>
+      <c r="P18">
+        <v>0.14234664304391501</v>
+      </c>
+      <c r="Q18">
+        <v>0.151607237164159</v>
+      </c>
+      <c r="R18">
+        <v>0.15727137430621099</v>
+      </c>
+      <c r="S18">
+        <v>0.19246036788809401</v>
+      </c>
+      <c r="T18">
+        <v>4.8595350736265398E-2</v>
+      </c>
+      <c r="U18">
+        <v>0.16563838382319401</v>
+      </c>
+      <c r="V18">
+        <v>0.13934921953752799</v>
+      </c>
+      <c r="W18">
+        <v>0.244301359875361</v>
+      </c>
+      <c r="X18">
+        <v>0.33383532782401898</v>
+      </c>
+      <c r="Y18">
+        <v>0.39947461074061302</v>
+      </c>
+      <c r="Z18">
+        <v>0.38493734584862999</v>
+      </c>
+      <c r="AA18">
+        <v>0.446402771593637</v>
+      </c>
+      <c r="AB18">
+        <v>0.49640854586813399</v>
+      </c>
+      <c r="AC18">
+        <v>0.53692286914190901</v>
+      </c>
+      <c r="AD18">
+        <v>0.524555305217557</v>
+      </c>
+      <c r="AE18">
+        <v>0.55669687643252497</v>
+      </c>
+      <c r="AF18">
+        <v>0.58567881559004997</v>
+      </c>
+      <c r="AG18">
+        <v>0.57046122976105995</v>
+      </c>
+      <c r="AH18">
+        <v>0.59642044768903502</v>
+      </c>
+      <c r="AI18">
+        <v>0.61392983895560105</v>
+      </c>
+      <c r="AJ18">
+        <v>0.60192690442979302</v>
+      </c>
+      <c r="AK18">
+        <v>0.61970370775537198</v>
+      </c>
+      <c r="AL18">
+        <v>0.63321385747959702</v>
+      </c>
+      <c r="AM18">
+        <v>0.62309446707410898</v>
+      </c>
+      <c r="AN18">
+        <v>0.63320231504269897</v>
+      </c>
+      <c r="AO18">
+        <v>0.64475528202462196</v>
+      </c>
+      <c r="AP18">
+        <v>0.63438435102631896</v>
+      </c>
+      <c r="AQ18">
+        <v>0.64319772882441495</v>
+      </c>
+      <c r="AR18">
+        <v>0.63328763971303303</v>
+      </c>
+      <c r="AS18">
+        <v>0.64089628244307795</v>
+      </c>
+      <c r="AT18">
+        <v>0.64761392291854003</v>
+      </c>
+      <c r="AU18">
+        <v>0.63883918847626697</v>
+      </c>
+      <c r="AV18">
+        <v>0.64505250387652102</v>
+      </c>
+      <c r="AW18">
+        <v>0.63693860178068595</v>
+      </c>
+      <c r="AX18">
+        <v>0.641600453808993</v>
+      </c>
+      <c r="AY18">
+        <v>0.63413167261605496</v>
+      </c>
+      <c r="AZ18">
+        <v>0.63874452090266198</v>
+      </c>
+      <c r="BA18">
+        <v>0.63118154551253502</v>
+      </c>
+      <c r="BB18">
+        <v>0.63517818049054797</v>
+      </c>
+      <c r="BC18">
+        <v>0.62814564112921401</v>
+      </c>
+      <c r="BD18">
+        <v>0.63157506559279897</v>
+      </c>
+      <c r="BE18">
+        <v>0.62448727996846598</v>
+      </c>
+      <c r="BF18">
+        <v>0.62747162642079202</v>
+      </c>
+      <c r="BG18">
+        <v>0.62082466915204604</v>
+      </c>
+      <c r="BH18">
+        <v>0.62339182809287996</v>
+      </c>
+      <c r="BI18">
+        <v>0.61739050606781298</v>
+      </c>
+    </row>
+    <row r="19" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>0.2282974593131</v>
+      </c>
+      <c r="C19">
+        <v>0.12889811620017</v>
+      </c>
+      <c r="D19">
+        <v>0.220534235534948</v>
+      </c>
+      <c r="E19">
+        <v>0.11729822953473799</v>
+      </c>
+      <c r="F19">
+        <v>0.24342899179577299</v>
+      </c>
+      <c r="G19">
+        <v>0.12981215457880799</v>
+      </c>
+      <c r="H19">
+        <v>6.6846470573987501E-2</v>
+      </c>
+      <c r="I19">
+        <v>0.121037041405477</v>
+      </c>
+      <c r="J19">
+        <v>5.7024816776137202E-2</v>
+      </c>
+      <c r="K19">
+        <v>6.7393300234775605E-2</v>
+      </c>
+      <c r="L19">
+        <v>6.4279706072193896E-2</v>
+      </c>
+      <c r="M19">
+        <v>7.5618459968588195E-2</v>
+      </c>
+      <c r="N19">
+        <v>0.128651638289625</v>
+      </c>
+      <c r="O19">
+        <v>0.13124194933421299</v>
+      </c>
+      <c r="P19">
+        <v>0.13487545753016</v>
+      </c>
+      <c r="Q19">
+        <v>0.13938007967838101</v>
+      </c>
+      <c r="R19">
+        <v>0.14460215918512101</v>
+      </c>
+      <c r="S19">
+        <v>0.15246664268177601</v>
+      </c>
+      <c r="T19">
+        <v>0.15723744045575999</v>
+      </c>
+      <c r="U19">
+        <v>0.16045131619969899</v>
+      </c>
+      <c r="V19">
+        <v>4.0234363447597198E-2</v>
+      </c>
+      <c r="W19">
+        <v>7.2255036393705493E-2</v>
+      </c>
+      <c r="X19">
+        <v>5.5488955439228001E-2</v>
+      </c>
+      <c r="Y19">
+        <v>0.12212726708497</v>
+      </c>
+      <c r="Z19">
+        <v>0.20664127090170101</v>
+      </c>
+      <c r="AA19">
+        <v>0.26497321648608202</v>
+      </c>
+      <c r="AB19">
+        <v>0.24242246001732001</v>
+      </c>
+      <c r="AC19">
+        <v>0.30882832432044899</v>
+      </c>
+      <c r="AD19">
+        <v>0.36688165107308202</v>
+      </c>
+      <c r="AE19">
+        <v>0.42178693042434401</v>
+      </c>
+      <c r="AF19">
+        <v>0.39836982867902998</v>
+      </c>
+      <c r="AG19">
+        <v>0.44115643922791797</v>
+      </c>
+      <c r="AH19">
+        <v>0.47792973508693098</v>
+      </c>
+      <c r="AI19">
+        <v>0.45992258224094101</v>
+      </c>
+      <c r="AJ19">
+        <v>0.491699783481229</v>
+      </c>
+      <c r="AK19">
+        <v>0.522069272790747</v>
+      </c>
+      <c r="AL19">
+        <v>0.50226397861031502</v>
+      </c>
+      <c r="AM19">
+        <v>0.52631927665290101</v>
+      </c>
+      <c r="AN19">
+        <v>0.549613058710265</v>
+      </c>
+      <c r="AO19">
+        <v>0.53404575058411696</v>
+      </c>
+      <c r="AP19">
+        <v>0.55240445165965202</v>
+      </c>
+      <c r="AQ19">
+        <v>0.53757916093509295</v>
+      </c>
+      <c r="AR19">
+        <v>0.55635905306103905</v>
+      </c>
+      <c r="AS19">
+        <v>0.57231590609213001</v>
+      </c>
+      <c r="AT19">
+        <v>0.55866562245780205</v>
+      </c>
+      <c r="AU19">
+        <v>0.57303322715656702</v>
+      </c>
+      <c r="AV19">
+        <v>0.56011624890522305</v>
+      </c>
+      <c r="AW19">
+        <v>0.57301130728551497</v>
+      </c>
+      <c r="AX19">
+        <v>0.58438684142403696</v>
+      </c>
+      <c r="AY19">
+        <v>0.57228936095086202</v>
+      </c>
+      <c r="AZ19">
+        <v>0.58390313295735696</v>
+      </c>
+      <c r="BA19">
+        <v>0.572333377980494</v>
+      </c>
+      <c r="BB19">
+        <v>0.58170756296346704</v>
+      </c>
+      <c r="BC19">
+        <v>0.57171603784887604</v>
+      </c>
+      <c r="BD19">
+        <v>0.58020863799537403</v>
+      </c>
+      <c r="BE19">
+        <v>0.56949736499958303</v>
+      </c>
+      <c r="BF19">
+        <v>0.57827978589605999</v>
+      </c>
+      <c r="BG19">
+        <v>0.56905705019877995</v>
+      </c>
+      <c r="BH19">
+        <v>0.57615960846666703</v>
+      </c>
+      <c r="BI19">
+        <v>0.56707434448860405</v>
+      </c>
+    </row>
+    <row r="20" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>0.25083966443427602</v>
+      </c>
+      <c r="C20">
+        <v>0.16120594674891001</v>
+      </c>
+      <c r="D20">
+        <v>0.22981831577141801</v>
+      </c>
+      <c r="E20">
+        <v>0.177698572498762</v>
+      </c>
+      <c r="F20">
+        <v>9.5163945003852599E-2</v>
+      </c>
+      <c r="G20">
+        <v>0.19076525511683201</v>
+      </c>
+      <c r="H20">
+        <v>6.6188452933541794E-2</v>
+      </c>
+      <c r="I20">
+        <v>0.12338359795477299</v>
+      </c>
+      <c r="J20">
+        <v>5.14647769515129E-2</v>
+      </c>
+      <c r="K20">
+        <v>5.1165938135709098E-2</v>
+      </c>
+      <c r="L20">
+        <v>5.5109886504304102E-2</v>
+      </c>
+      <c r="M20">
+        <v>0.103512669064593</v>
+      </c>
+      <c r="N20">
+        <v>9.5390935575846394E-2</v>
+      </c>
+      <c r="O20">
+        <v>0.104967592518281</v>
+      </c>
+      <c r="P20">
+        <v>0.17078925266495501</v>
+      </c>
+      <c r="Q20">
+        <v>0.134456024986956</v>
+      </c>
+      <c r="R20">
+        <v>0.13788535149651199</v>
+      </c>
+      <c r="S20">
+        <v>0.14193993769522101</v>
+      </c>
+      <c r="T20">
+        <v>0.146097594204501</v>
+      </c>
+      <c r="U20">
+        <v>0.150593612909763</v>
+      </c>
+      <c r="V20">
+        <v>0.15621018790423</v>
+      </c>
+      <c r="W20">
+        <v>0.15985546246423599</v>
+      </c>
+      <c r="X20">
+        <v>0.106785812853628</v>
+      </c>
+      <c r="Y20">
+        <v>3.32354779196396E-2</v>
+      </c>
+      <c r="Z20">
+        <v>0.11832725269937</v>
+      </c>
+      <c r="AA20">
+        <v>3.4324650512184703E-2</v>
+      </c>
+      <c r="AB20">
+        <v>8.6052767715292994E-2</v>
+      </c>
+      <c r="AC20">
+        <v>0.15878304481206901</v>
+      </c>
+      <c r="AD20">
+        <v>0.134217787864821</v>
+      </c>
+      <c r="AE20">
+        <v>0.181165421030651</v>
+      </c>
+      <c r="AF20">
+        <v>0.23916823391056899</v>
+      </c>
+      <c r="AG20">
+        <v>0.21421026073067201</v>
+      </c>
+      <c r="AH20">
+        <v>0.25490133821170302</v>
+      </c>
+      <c r="AI20">
+        <v>0.30726270166380298</v>
+      </c>
+      <c r="AJ20">
+        <v>0.35416327077360399</v>
+      </c>
+      <c r="AK20">
+        <v>0.32498895258645</v>
+      </c>
+      <c r="AL20">
+        <v>0.36722234080536498</v>
+      </c>
+      <c r="AM20">
+        <v>0.39612627374778803</v>
+      </c>
+      <c r="AN20">
+        <v>0.37230326254908203</v>
+      </c>
+      <c r="AO20">
+        <v>0.40747472162678799</v>
+      </c>
+      <c r="AP20">
+        <v>0.38476017453092798</v>
+      </c>
+      <c r="AQ20">
+        <v>0.413395793695016</v>
+      </c>
+      <c r="AR20">
+        <v>0.442100233019324</v>
+      </c>
+      <c r="AS20">
+        <v>0.42093579687429</v>
+      </c>
+      <c r="AT20">
+        <v>0.44145086954761598</v>
+      </c>
+      <c r="AU20">
+        <v>0.46563780392109799</v>
+      </c>
+      <c r="AV20">
+        <v>0.44581034292245098</v>
+      </c>
+      <c r="AW20">
+        <v>0.46806352411255397</v>
+      </c>
+      <c r="AX20">
+        <v>0.449102548776104</v>
+      </c>
+      <c r="AY20">
+        <v>0.46966675922310802</v>
+      </c>
+      <c r="AZ20">
+        <v>0.45149790717576999</v>
+      </c>
+      <c r="BA20">
+        <v>0.47057705140987899</v>
+      </c>
+      <c r="BB20">
+        <v>0.48987634909857097</v>
+      </c>
+      <c r="BC20">
+        <v>0.472983641750293</v>
+      </c>
+      <c r="BD20">
+        <v>0.48895807455638601</v>
+      </c>
+      <c r="BE20">
+        <v>0.47269882740485503</v>
+      </c>
+      <c r="BF20">
+        <v>0.48766954855903699</v>
+      </c>
+      <c r="BG20">
+        <v>0.47199399901060202</v>
+      </c>
+      <c r="BH20">
+        <v>0.48606329998467002</v>
+      </c>
+      <c r="BI20">
+        <v>0.47271771629799603</v>
+      </c>
+    </row>
+    <row r="21" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>0.27650630629542799</v>
+      </c>
+      <c r="C21">
+        <v>0.22386821691431799</v>
+      </c>
+      <c r="D21">
+        <v>0.15759630509606201</v>
+      </c>
+      <c r="E21">
+        <v>0.18745450369123201</v>
+      </c>
+      <c r="F21">
+        <v>0.13364126288435099</v>
+      </c>
+      <c r="G21">
+        <v>0.19656831534041</v>
+      </c>
+      <c r="H21">
+        <v>0.150577510333404</v>
+      </c>
+      <c r="I21">
+        <v>5.5229761848252797E-2</v>
+      </c>
+      <c r="J21">
+        <v>9.3215562883828304E-2</v>
+      </c>
+      <c r="K21">
+        <v>4.3635982596311802E-2</v>
+      </c>
+      <c r="L21">
+        <v>4.8318754218289302E-2</v>
+      </c>
+      <c r="M21">
+        <v>9.2707320184201095E-2</v>
+      </c>
+      <c r="N21">
+        <v>8.0793748817774694E-2</v>
+      </c>
+      <c r="O21">
+        <v>9.5656627027040295E-2</v>
+      </c>
+      <c r="P21">
+        <v>0.13125979268705601</v>
+      </c>
+      <c r="Q21">
+        <v>0.14911218938394699</v>
+      </c>
+      <c r="R21">
+        <v>0.12907334852052299</v>
+      </c>
+      <c r="S21">
+        <v>0.13755299779123201</v>
+      </c>
+      <c r="T21">
+        <v>0.140347097721151</v>
+      </c>
+      <c r="U21">
+        <v>0.14349324753762499</v>
+      </c>
+      <c r="V21">
+        <v>0.14689501702510499</v>
+      </c>
+      <c r="W21">
+        <v>0.150766722127994</v>
+      </c>
+      <c r="X21">
+        <v>0.155180225310388</v>
+      </c>
+      <c r="Y21">
+        <v>0.15808184670973499</v>
+      </c>
+      <c r="Z21">
+        <v>0.16127314431585299</v>
+      </c>
+      <c r="AA21">
+        <v>6.2749374980183806E-2</v>
+      </c>
+      <c r="AB21">
+        <v>0.16685554758066301</v>
+      </c>
+      <c r="AC21">
+        <v>3.9205068128716603E-2</v>
+      </c>
+      <c r="AD21">
+        <v>2.70263093957782E-2</v>
+      </c>
+      <c r="AE21">
+        <v>6.4476597644559305E-2</v>
+      </c>
+      <c r="AF21">
+        <v>3.9925200152320997E-2</v>
+      </c>
+      <c r="AG21">
+        <v>7.9821227013167198E-2</v>
+      </c>
+      <c r="AH21">
+        <v>0.14272673447786199</v>
+      </c>
+      <c r="AI21">
+        <v>9.0984629331266498E-2</v>
+      </c>
+      <c r="AJ21">
+        <v>0.152025093081606</v>
+      </c>
+      <c r="AK21">
+        <v>0.20344125364062501</v>
+      </c>
+      <c r="AL21">
+        <v>0.15754965229027301</v>
+      </c>
+      <c r="AM21">
+        <v>0.20876737057385999</v>
+      </c>
+      <c r="AN21">
+        <v>0.23560828330873801</v>
+      </c>
+      <c r="AO21">
+        <v>0.21061968080429599</v>
+      </c>
+      <c r="AP21">
+        <v>0.25485163488742602</v>
+      </c>
+      <c r="AQ21">
+        <v>0.27852432936382798</v>
+      </c>
+      <c r="AR21">
+        <v>0.25407903675242999</v>
+      </c>
+      <c r="AS21">
+        <v>0.292762009560042</v>
+      </c>
+      <c r="AT21">
+        <v>0.31371545317889399</v>
+      </c>
+      <c r="AU21">
+        <v>0.290030644976976</v>
+      </c>
+      <c r="AV21">
+        <v>0.32404402613483502</v>
+      </c>
+      <c r="AW21">
+        <v>0.29005309554735798</v>
+      </c>
+      <c r="AX21">
+        <v>0.319842268092773</v>
+      </c>
+      <c r="AY21">
+        <v>0.349854037945311</v>
+      </c>
+      <c r="AZ21">
+        <v>0.31832704191958899</v>
+      </c>
+      <c r="BA21">
+        <v>0.34711465771786498</v>
+      </c>
+      <c r="BB21">
+        <v>0.32329239436045298</v>
+      </c>
+      <c r="BC21">
+        <v>0.34184636210505898</v>
+      </c>
+      <c r="BD21">
+        <v>0.36742075712865602</v>
+      </c>
+      <c r="BE21">
+        <v>0.34704063896252202</v>
+      </c>
+      <c r="BF21">
+        <v>0.36868736943423402</v>
+      </c>
+      <c r="BG21">
+        <v>0.34154922754611899</v>
+      </c>
+      <c r="BH21">
+        <v>0.36473671142279501</v>
+      </c>
+      <c r="BI21">
+        <v>0.34559317630069403</v>
+      </c>
+    </row>
+    <row r="22" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>0.35885566376565298</v>
+      </c>
+      <c r="C22">
+        <v>0.21664313683567199</v>
+      </c>
+      <c r="D22">
+        <v>0.176504724523805</v>
+      </c>
+      <c r="E22">
+        <v>0.200007723458311</v>
+      </c>
+      <c r="F22">
+        <v>0.15716507454600601</v>
+      </c>
+      <c r="G22">
+        <v>8.51812304994648E-2</v>
+      </c>
+      <c r="H22">
+        <v>0.15572232336980099</v>
+      </c>
+      <c r="I22">
+        <v>0.18287804430100199</v>
+      </c>
+      <c r="J22">
+        <v>9.5193301468754002E-2</v>
+      </c>
+      <c r="K22">
+        <v>0.21088637128851501</v>
+      </c>
+      <c r="L22">
+        <v>3.67112288458461E-2</v>
+      </c>
+      <c r="M22">
+        <v>4.1024500265500002E-2</v>
+      </c>
+      <c r="N22">
+        <v>6.5948651708950604E-2</v>
+      </c>
+      <c r="O22">
+        <v>6.0948703128095201E-2</v>
+      </c>
+      <c r="P22">
+        <v>4.9749579555789902E-2</v>
+      </c>
+      <c r="Q22">
+        <v>8.9242925663843994E-2</v>
+      </c>
+      <c r="R22">
+        <v>0.11140220638548901</v>
+      </c>
+      <c r="S22">
+        <v>0.11995995716832</v>
+      </c>
+      <c r="T22">
+        <v>0.13830244377770701</v>
+      </c>
+      <c r="U22">
+        <v>0.14072284869226001</v>
+      </c>
+      <c r="V22">
+        <v>0.14379973218995901</v>
+      </c>
+      <c r="W22">
+        <v>0.14599685077573399</v>
+      </c>
+      <c r="X22">
+        <v>0.149060510747067</v>
+      </c>
+      <c r="Y22">
+        <v>0.37695928172885901</v>
+      </c>
+      <c r="Z22">
+        <v>0.15420197714933501</v>
+      </c>
+      <c r="AA22">
+        <v>0.15721511564776</v>
+      </c>
+      <c r="AB22">
+        <v>0.16040120353619999</v>
+      </c>
+      <c r="AC22">
+        <v>0.150609487734431</v>
+      </c>
+      <c r="AD22">
+        <v>0.21691098454053101</v>
+      </c>
+      <c r="AE22">
+        <v>0.10619101439522501</v>
+      </c>
+      <c r="AF22">
+        <v>5.4117151325379802E-2</v>
+      </c>
+      <c r="AG22">
+        <v>4.2392617817515202E-2</v>
+      </c>
+      <c r="AH22">
+        <v>3.6413402566383403E-2</v>
+      </c>
+      <c r="AI22">
+        <v>1.6381342425366999E-2</v>
+      </c>
+      <c r="AJ22">
+        <v>8.1350924772817204E-2</v>
+      </c>
+      <c r="AK22">
+        <v>2.3703870840446901E-2</v>
+      </c>
+      <c r="AL22">
+        <v>8.6878892488213899E-2</v>
+      </c>
+      <c r="AM22">
+        <v>0.115242140004598</v>
+      </c>
+      <c r="AN22">
+        <v>6.1869794625088799E-2</v>
+      </c>
+      <c r="AO22">
+        <v>0.118021702313754</v>
+      </c>
+      <c r="AP22">
+        <v>0.14421197246785</v>
+      </c>
+      <c r="AQ22">
+        <v>0.120829273171583</v>
+      </c>
+      <c r="AR22">
+        <v>0.145949608289525</v>
+      </c>
+      <c r="AS22">
+        <v>0.19148799858391399</v>
+      </c>
+      <c r="AT22">
+        <v>0.145943394145367</v>
+      </c>
+      <c r="AU22">
+        <v>0.18923283214806499</v>
+      </c>
+      <c r="AV22">
+        <v>0.210787433998987</v>
+      </c>
+      <c r="AW22">
+        <v>0.18805124169258899</v>
+      </c>
+      <c r="AX22">
+        <v>0.208884646146237</v>
+      </c>
+      <c r="AY22">
+        <v>0.168997802794878</v>
+      </c>
+      <c r="AZ22">
+        <v>0.20529356520536099</v>
+      </c>
+      <c r="BA22">
+        <v>0.22496661554257799</v>
+      </c>
+      <c r="BB22">
+        <v>0.20313045200959601</v>
+      </c>
+      <c r="BC22">
+        <v>0.22217514708335301</v>
+      </c>
+      <c r="BD22">
+        <v>0.20087380016989601</v>
+      </c>
+      <c r="BE22">
+        <v>0.219321229545763</v>
+      </c>
+      <c r="BF22">
+        <v>0.24895887188622301</v>
+      </c>
+      <c r="BG22">
+        <v>0.21471473362183499</v>
+      </c>
+      <c r="BH22">
+        <v>0.24494948207175901</v>
+      </c>
+      <c r="BI22">
+        <v>0.21174975941697899</v>
+      </c>
+    </row>
+    <row r="23" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>0.66417653019743095</v>
+      </c>
+      <c r="C23">
+        <v>0.339269579650537</v>
+      </c>
+      <c r="D23">
+        <v>0.17898354400449901</v>
+      </c>
+      <c r="E23">
+        <v>0.17404196616683501</v>
+      </c>
+      <c r="F23">
+        <v>0.16870697901326301</v>
+      </c>
+      <c r="G23">
+        <v>0.67172377506277303</v>
+      </c>
+      <c r="H23">
+        <v>0.16269336647518701</v>
+      </c>
+      <c r="I23">
+        <v>7.1369177422831095E-2</v>
+      </c>
+      <c r="J23">
+        <v>4.5824766271245702E-2</v>
+      </c>
+      <c r="K23">
+        <v>7.1618023232838002E-2</v>
+      </c>
+      <c r="L23">
+        <v>0.16505096652290099</v>
+      </c>
+      <c r="M23">
+        <v>4.9046353427290801E-2</v>
+      </c>
+      <c r="N23">
+        <v>6.4902744570223006E-2</v>
+      </c>
+      <c r="O23">
+        <v>4.8691454405143199E-2</v>
+      </c>
+      <c r="P23">
+        <v>4.5854924960387802E-2</v>
+      </c>
+      <c r="Q23">
+        <v>4.2232585404265298E-2</v>
+      </c>
+      <c r="R23">
+        <v>4.4214497240126202E-2</v>
+      </c>
+      <c r="S23">
+        <v>3.3064155143364297E-2</v>
+      </c>
+      <c r="T23">
+        <v>0.41413262191872802</v>
+      </c>
+      <c r="U23">
+        <v>0.31719854531110903</v>
+      </c>
+      <c r="V23">
+        <v>0.62555115753005097</v>
+      </c>
+      <c r="W23">
+        <v>0.35884535760914099</v>
+      </c>
+      <c r="X23">
+        <v>0.145764719450137</v>
+      </c>
+      <c r="Y23">
+        <v>0.14790148573224901</v>
+      </c>
+      <c r="Z23">
+        <v>0.15046010740101601</v>
+      </c>
+      <c r="AA23">
+        <v>0.15323400967060199</v>
+      </c>
+      <c r="AB23">
+        <v>0.15521835435775799</v>
+      </c>
+      <c r="AC23">
+        <v>0.25053325505308899</v>
+      </c>
+      <c r="AD23">
+        <v>0.12333066588962401</v>
+      </c>
+      <c r="AE23">
+        <v>8.7265773280045006E-2</v>
+      </c>
+      <c r="AF23">
+        <v>0.165605216604434</v>
+      </c>
+      <c r="AG23">
+        <v>0.15095335834667001</v>
+      </c>
+      <c r="AH23">
+        <v>8.8735728909400902E-2</v>
+      </c>
+      <c r="AI23">
+        <v>0.101279170210896</v>
+      </c>
+      <c r="AJ23">
+        <v>6.6782817939651504E-2</v>
+      </c>
+      <c r="AK23">
+        <v>2.9610297007474001E-2</v>
+      </c>
+      <c r="AL23">
+        <v>1.1704428228770301E-2</v>
+      </c>
+      <c r="AM23">
+        <v>1.51520939455376E-2</v>
+      </c>
+      <c r="AN23">
+        <v>2.2931771334237301E-2</v>
+      </c>
+      <c r="AO23">
+        <v>4.7532606224317597E-2</v>
+      </c>
+      <c r="AP23">
+        <v>3.0467795249578999E-2</v>
+      </c>
+      <c r="AQ23">
+        <v>5.6441502311139098E-2</v>
+      </c>
+      <c r="AR23">
+        <v>8.1823091878088297E-2</v>
+      </c>
+      <c r="AS23">
+        <v>2.95568372085535E-2</v>
+      </c>
+      <c r="AT23">
+        <v>8.7347626482472102E-2</v>
+      </c>
+      <c r="AU23">
+        <v>0.108955673685575</v>
+      </c>
+      <c r="AV23">
+        <v>6.0420146378213802E-2</v>
+      </c>
+      <c r="AW23">
+        <v>0.112000143015256</v>
+      </c>
+      <c r="AX23">
+        <v>6.57685156209636E-2</v>
+      </c>
+      <c r="AY23">
+        <v>8.7828004444680502E-2</v>
+      </c>
+      <c r="AZ23">
+        <v>0.13411133012114099</v>
+      </c>
+      <c r="BA23">
+        <v>9.0151421387881098E-2</v>
+      </c>
+      <c r="BB23">
+        <v>0.11050755716286299</v>
+      </c>
+      <c r="BC23">
+        <v>0.15249735747369</v>
+      </c>
+      <c r="BD23">
+        <v>0.111783146909435</v>
+      </c>
+      <c r="BE23">
+        <v>0.13044267392525</v>
+      </c>
+      <c r="BF23">
+        <v>0.11264877800574701</v>
+      </c>
+      <c r="BG23">
+        <v>0.130340879573727</v>
+      </c>
+      <c r="BH23">
+        <v>0.14757931542970201</v>
+      </c>
+      <c r="BI23">
+        <v>0.129727241881683</v>
+      </c>
+    </row>
+    <row r="24" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>0.53997434077111905</v>
+      </c>
+      <c r="D24">
+        <v>0.26032721205346898</v>
+      </c>
+      <c r="E24">
+        <v>0.221011552495782</v>
+      </c>
+      <c r="F24">
+        <v>0.17475356935325401</v>
+      </c>
+      <c r="G24">
+        <v>0.15139979486928401</v>
+      </c>
+      <c r="H24">
+        <v>0.46401197959206297</v>
+      </c>
+      <c r="I24">
+        <v>0.12971394012642701</v>
+      </c>
+      <c r="J24">
+        <v>0.149303895393049</v>
+      </c>
+      <c r="K24">
+        <v>7.2801911469450198E-2</v>
+      </c>
+      <c r="L24">
+        <v>5.5907218947782597E-2</v>
+      </c>
+      <c r="M24">
+        <v>3.3318628721311798E-2</v>
+      </c>
+      <c r="N24">
+        <v>3.6792200799874303E-2</v>
+      </c>
+      <c r="O24">
+        <v>4.3678314919905703E-2</v>
+      </c>
+      <c r="P24">
+        <v>3.1338007816856001E-2</v>
+      </c>
+      <c r="Q24">
+        <v>4.1762012796723001E-2</v>
+      </c>
+      <c r="R24">
+        <v>4.5007292855438898E-2</v>
+      </c>
+      <c r="S24">
+        <v>3.7842709540897898E-2</v>
+      </c>
+      <c r="T24">
+        <v>8.2497928783353006E-2</v>
+      </c>
+      <c r="U24">
+        <v>6.6242128827660604E-2</v>
+      </c>
+      <c r="V24">
+        <v>0.150587251301288</v>
+      </c>
+      <c r="W24">
+        <v>0.13061635862246501</v>
+      </c>
+      <c r="X24">
+        <v>0.13791695919615099</v>
+      </c>
+      <c r="Y24">
+        <v>8.81659097974999E-2</v>
+      </c>
+      <c r="Z24">
+        <v>0.52471879900065999</v>
+      </c>
+      <c r="AA24">
+        <v>0.35686063595145701</v>
+      </c>
+      <c r="AB24">
+        <v>0.13572713757763</v>
+      </c>
+      <c r="AC24">
+        <v>0.10422582122603601</v>
+      </c>
+      <c r="AD24">
+        <v>0.157465857277751</v>
+      </c>
+      <c r="AE24">
+        <v>0.329894942505014</v>
+      </c>
+      <c r="AF24">
+        <v>0.124035057874121</v>
+      </c>
+      <c r="AG24">
+        <v>8.6107785966846095E-2</v>
+      </c>
+      <c r="AH24">
+        <v>0.39425526496876701</v>
+      </c>
+      <c r="AI24">
+        <v>0.15775983296181101</v>
+      </c>
+      <c r="AJ24">
+        <v>9.0437566432837901E-2</v>
+      </c>
+      <c r="AK24">
+        <v>9.5625867902997194E-2</v>
+      </c>
+      <c r="AL24">
+        <v>6.3832140027824003E-2</v>
+      </c>
+      <c r="AM24">
+        <v>2.545280849335E-2</v>
+      </c>
+      <c r="AN24">
+        <v>7.6179441224596897E-3</v>
+      </c>
+      <c r="AO24">
+        <v>6.4658972469698997E-2</v>
+      </c>
+      <c r="AP24">
+        <v>3.4617072051446797E-2</v>
+      </c>
+      <c r="AQ24">
+        <v>4.81465634352626E-2</v>
+      </c>
+      <c r="AR24">
+        <v>1.3105923528985999E-2</v>
+      </c>
+      <c r="AS24">
+        <v>1.4971315906306499E-2</v>
+      </c>
+      <c r="AT24">
+        <v>4.3580351219339897E-2</v>
+      </c>
+      <c r="AU24">
+        <v>1.3657661387192E-2</v>
+      </c>
+      <c r="AV24">
+        <v>1.29574858277096E-2</v>
+      </c>
+      <c r="AW24">
+        <v>7.8057264196648393E-2</v>
+      </c>
+      <c r="AX24">
+        <v>2.7540592630905501E-2</v>
+      </c>
+      <c r="AY24">
+        <v>4.9022877353041297E-2</v>
+      </c>
+      <c r="AZ24">
+        <v>5.9514487653424498E-3</v>
+      </c>
+      <c r="BA24">
+        <v>2.5239378788921001E-2</v>
+      </c>
+      <c r="BB24">
+        <v>7.9294049010590506E-2</v>
+      </c>
+      <c r="BC24">
+        <v>3.6707398977363498E-2</v>
+      </c>
+      <c r="BD24">
+        <v>5.6249108935628699E-2</v>
+      </c>
+      <c r="BE24">
+        <v>7.8345559110765295E-2</v>
+      </c>
+      <c r="BF24">
+        <v>3.4079859903139199E-2</v>
+      </c>
+      <c r="BG24">
+        <v>5.3460090865013403E-2</v>
+      </c>
+      <c r="BH24">
+        <v>0.102579320301132</v>
+      </c>
+      <c r="BI24">
+        <v>6.1037918747809901E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>0.48701046821119898</v>
+      </c>
+      <c r="E25">
+        <v>0.64518826517250805</v>
+      </c>
+      <c r="F25">
+        <v>0.19826178026078101</v>
+      </c>
+      <c r="G25">
+        <v>0.47797512070357501</v>
+      </c>
+      <c r="H25">
+        <v>0.154707546418486</v>
+      </c>
+      <c r="I25">
+        <v>0.14377095944515</v>
+      </c>
+      <c r="J25">
+        <v>6.0042122760347101E-2</v>
+      </c>
+      <c r="K25">
+        <v>0.115366973440828</v>
+      </c>
+      <c r="L25">
+        <v>5.3489882661882003E-2</v>
+      </c>
+      <c r="M25">
+        <v>0.13069307222463999</v>
+      </c>
+      <c r="N25">
+        <v>5.8645905862148101E-2</v>
+      </c>
+      <c r="O25">
+        <v>2.8513035944048699E-2</v>
+      </c>
+      <c r="P25">
+        <v>5.45813882965928E-2</v>
+      </c>
+      <c r="Q25">
+        <v>2.9043264083073801E-2</v>
+      </c>
+      <c r="R25">
+        <v>2.7209575891984299E-2</v>
+      </c>
+      <c r="S25">
+        <v>2.7011541237626901E-2</v>
+      </c>
+      <c r="T25">
+        <v>5.8627294054608897E-2</v>
+      </c>
+      <c r="U25">
+        <v>6.3616707227500596E-2</v>
+      </c>
+      <c r="V25">
+        <v>5.56703281713204E-2</v>
+      </c>
+      <c r="W25">
+        <v>3.7519248068235499E-2</v>
+      </c>
+      <c r="X25">
+        <v>0.103474126720502</v>
+      </c>
+      <c r="Y25">
+        <v>8.6242130124669802E-2</v>
+      </c>
+      <c r="Z25">
+        <v>6.0280542285139502E-2</v>
+      </c>
+      <c r="AA25">
+        <v>0.124727736453825</v>
+      </c>
+      <c r="AB25">
+        <v>0.15315767238907499</v>
+      </c>
+      <c r="AC25">
+        <v>0.24966929530700299</v>
+      </c>
+      <c r="AD25">
+        <v>0.14703639350262401</v>
+      </c>
+      <c r="AE25">
+        <v>0.12631319460589399</v>
+      </c>
+      <c r="AF25">
+        <v>0.35510798706277202</v>
+      </c>
+      <c r="AG25">
+        <v>0.15595304504214499</v>
+      </c>
+      <c r="AH25">
+        <v>0.12698000026036199</v>
+      </c>
+      <c r="AI25">
+        <v>7.8198091653737395E-2</v>
+      </c>
+      <c r="AJ25">
+        <v>0.153559188610143</v>
+      </c>
+      <c r="AK25">
+        <v>0.12212294873252499</v>
+      </c>
+      <c r="AL25">
+        <v>7.6333369882656502E-2</v>
+      </c>
+      <c r="AM25">
+        <v>0.14554810617825401</v>
+      </c>
+      <c r="AN25">
+        <v>0.114883011342982</v>
+      </c>
+      <c r="AO25">
+        <v>1.0040531927098899E-2</v>
+      </c>
+      <c r="AP25">
+        <v>6.2806344698987396E-2</v>
+      </c>
+      <c r="AQ25">
+        <v>4.1523563791379003E-2</v>
+      </c>
+      <c r="AR25">
+        <v>9.8755349998814503E-3</v>
+      </c>
+      <c r="AS25">
+        <v>2.18497144005835E-2</v>
+      </c>
+      <c r="AT25">
+        <v>3.9655258877384997E-2</v>
+      </c>
+      <c r="AU25">
+        <v>9.0192576521851402E-3</v>
+      </c>
+      <c r="AV25">
+        <v>2.0837487730316601E-2</v>
+      </c>
+      <c r="AW25">
+        <v>3.7159304259881898E-2</v>
+      </c>
+      <c r="AX25">
+        <v>7.6874051076871001E-3</v>
+      </c>
+      <c r="AY25">
+        <v>2.05536770801668E-2</v>
+      </c>
+      <c r="AZ25">
+        <v>2.6618226403807201E-2</v>
+      </c>
+      <c r="BA25">
+        <v>6.0994930158491901E-3</v>
+      </c>
+      <c r="BB25">
+        <v>2.0754784471609999E-2</v>
+      </c>
+      <c r="BC25">
+        <v>2.4587382451681801E-2</v>
+      </c>
+      <c r="BD25">
+        <v>4.2246488328919099E-2</v>
+      </c>
+      <c r="BE25">
+        <v>7.5436381765144004E-3</v>
+      </c>
+      <c r="BF25">
+        <v>1.7336121348602299E-2</v>
+      </c>
+      <c r="BG25">
+        <v>4.0673097261359002E-2</v>
+      </c>
+      <c r="BH25">
+        <v>2.7008764404661901E-3</v>
+      </c>
+      <c r="BI25">
+        <v>2.2569623667617101E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>0.69647681489024804</v>
+      </c>
+      <c r="F26">
+        <v>0.23938762318753701</v>
+      </c>
+      <c r="G26">
+        <v>0.184000962802471</v>
+      </c>
+      <c r="H26">
+        <v>0.10306977472764101</v>
+      </c>
+      <c r="I26">
+        <v>0.126159265796396</v>
+      </c>
+      <c r="J26">
+        <v>6.5752378059138597E-2</v>
+      </c>
+      <c r="K26">
+        <v>0.12136400919929</v>
+      </c>
+      <c r="L26">
+        <v>5.42386808133574E-2</v>
+      </c>
+      <c r="M26">
+        <v>3.9109890726031098E-2</v>
+      </c>
+      <c r="N26">
+        <v>9.6353297021007395E-2</v>
+      </c>
+      <c r="O26">
+        <v>4.0348639868132599E-2</v>
+      </c>
+      <c r="P26">
+        <v>5.2475887820176398E-2</v>
+      </c>
+      <c r="Q26">
+        <v>0.14989515710806101</v>
+      </c>
+      <c r="R26">
+        <v>2.64111359735913E-2</v>
+      </c>
+      <c r="S26">
+        <v>2.7438722119666799E-2</v>
+      </c>
+      <c r="T26">
+        <v>3.0144916200959899E-2</v>
+      </c>
+      <c r="U26">
+        <v>4.1016961174267397E-2</v>
+      </c>
+      <c r="V26">
+        <v>5.2149143216914301E-2</v>
+      </c>
+      <c r="W26">
+        <v>4.7145759173962902E-2</v>
+      </c>
+      <c r="X26">
+        <v>3.2636347489837202E-2</v>
+      </c>
+      <c r="Y26">
+        <v>7.8624226565906299E-2</v>
+      </c>
+      <c r="Z26">
+        <v>5.9591008562993403E-2</v>
+      </c>
+      <c r="AA26">
+        <v>0.102132206744769</v>
+      </c>
+      <c r="AB26">
+        <v>8.4325340469200594E-2</v>
+      </c>
+      <c r="AC26">
+        <v>5.87651624596085E-2</v>
+      </c>
+      <c r="AD26">
+        <v>2.93645832609397E-2</v>
+      </c>
+      <c r="AE26">
+        <v>8.2746677511237696E-2</v>
+      </c>
+      <c r="AF26">
+        <v>5.40116140571733E-2</v>
+      </c>
+      <c r="AG26">
+        <v>2.3708965334316299E-2</v>
+      </c>
+      <c r="AH26">
+        <v>0.17270943500563599</v>
+      </c>
+      <c r="AI26">
+        <v>0.12887594718023601</v>
+      </c>
+      <c r="AJ26">
+        <v>9.2118890576275606E-2</v>
+      </c>
+      <c r="AK26">
+        <v>5.75548144516249E-2</v>
+      </c>
+      <c r="AL26">
+        <v>0.113662974485254</v>
+      </c>
+      <c r="AM26">
+        <v>7.9223524594798103E-2</v>
+      </c>
+      <c r="AN26">
+        <v>6.32927112738111E-2</v>
+      </c>
+      <c r="AO26">
+        <v>0.119263519309355</v>
+      </c>
+      <c r="AP26">
+        <v>8.3787257756955197E-2</v>
+      </c>
+      <c r="AQ26">
+        <v>5.0619371379259197E-2</v>
+      </c>
+      <c r="AR26">
+        <v>0.103045470203316</v>
+      </c>
+      <c r="AS26">
+        <v>7.0439128922866107E-2</v>
+      </c>
+      <c r="AT26">
+        <v>3.9215731647818997E-2</v>
+      </c>
+      <c r="AU26">
+        <v>9.0083961496983597E-3</v>
+      </c>
+      <c r="AV26">
+        <v>5.85160219777432E-2</v>
+      </c>
+      <c r="AW26">
+        <v>2.8990436348509101E-2</v>
+      </c>
+      <c r="AX26">
+        <v>1.4777294197625399E-3</v>
+      </c>
+      <c r="AY26">
+        <v>3.6165878890247201E-2</v>
+      </c>
+      <c r="AZ26">
+        <v>8.8661623867587903E-3</v>
+      </c>
+      <c r="BA26">
+        <v>1.7792392753933801E-2</v>
+      </c>
+      <c r="BB26">
+        <v>2.76868440574475E-2</v>
+      </c>
+      <c r="BC26">
+        <v>1.6360295700341501E-3</v>
+      </c>
+      <c r="BD26">
+        <v>2.3782676057084801E-2</v>
+      </c>
+      <c r="BE26">
+        <v>2.0045843370125799E-2</v>
+      </c>
+      <c r="BF26">
+        <v>4.8339839843664998E-3</v>
+      </c>
+      <c r="BG26">
+        <v>2.9098157475785699E-2</v>
+      </c>
+      <c r="BH26">
+        <v>1.31851750463002E-2</v>
+      </c>
+      <c r="BI26">
+        <v>1.0600697553782099E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>0.63197406463616601</v>
+      </c>
+      <c r="G27">
+        <v>0.218304927637059</v>
+      </c>
+      <c r="H27">
+        <v>0.38882562877295601</v>
+      </c>
+      <c r="I27">
+        <v>0.13927711719380001</v>
+      </c>
+      <c r="J27">
+        <v>0.105388141734897</v>
+      </c>
+      <c r="K27">
+        <v>5.3209720074631303E-2</v>
+      </c>
+      <c r="L27">
+        <v>9.0220366937700303E-2</v>
+      </c>
+      <c r="M27">
+        <v>3.6622386066362297E-2</v>
+      </c>
+      <c r="N27">
+        <v>9.9678964933171799E-2</v>
+      </c>
+      <c r="O27">
+        <v>0.307567489775325</v>
+      </c>
+      <c r="P27">
+        <v>2.9646855349816599E-2</v>
+      </c>
+      <c r="Q27">
+        <v>3.2200728659727701E-2</v>
+      </c>
+      <c r="R27">
+        <v>1.8565007546755701E-2</v>
+      </c>
+      <c r="S27">
+        <v>4.1955536781265602E-2</v>
+      </c>
+      <c r="T27">
+        <v>2.8472887557489099E-2</v>
+      </c>
+      <c r="U27">
+        <v>3.7228911468663001E-2</v>
+      </c>
+      <c r="V27">
+        <v>3.4886832605636402E-2</v>
+      </c>
+      <c r="W27">
+        <v>2.2748439804431999E-2</v>
+      </c>
+      <c r="X27">
+        <v>4.2573511364348997E-2</v>
+      </c>
+      <c r="Y27">
+        <v>7.02510649904107E-2</v>
+      </c>
+      <c r="Z27">
+        <v>6.7383027828194303E-2</v>
+      </c>
+      <c r="AA27">
+        <v>3.2670575131134298E-2</v>
+      </c>
+      <c r="AB27">
+        <v>1.1427260776581001E-2</v>
+      </c>
+      <c r="AC27">
+        <v>5.6413938732652699E-2</v>
+      </c>
+      <c r="AD27">
+        <v>0.101584124738096</v>
+      </c>
+      <c r="AE27">
+        <v>8.3254563379519295E-2</v>
+      </c>
+      <c r="AF27">
+        <v>3.5023991468345402E-2</v>
+      </c>
+      <c r="AG27">
+        <v>8.3112809202567695E-2</v>
+      </c>
+      <c r="AH27">
+        <v>5.9245770973422401E-2</v>
+      </c>
+      <c r="AI27">
+        <v>3.14827282882622E-2</v>
+      </c>
+      <c r="AJ27">
+        <v>8.1212981705233195E-2</v>
+      </c>
+      <c r="AK27">
+        <v>0.10564535724543</v>
+      </c>
+      <c r="AL27">
+        <v>7.8736857402782398E-2</v>
+      </c>
+      <c r="AM27">
+        <v>4.9625764553225003E-2</v>
+      </c>
+      <c r="AN27">
+        <v>9.9168817350011804E-2</v>
+      </c>
+      <c r="AO27">
+        <v>7.1107331477460206E-2</v>
+      </c>
+      <c r="AP27">
+        <v>2.36810613232896E-2</v>
+      </c>
+      <c r="AQ27">
+        <v>7.2932327232485702E-2</v>
+      </c>
+      <c r="AR27">
+        <v>4.5498359904964099E-2</v>
+      </c>
+      <c r="AS27">
+        <v>1.71880380775708E-2</v>
+      </c>
+      <c r="AT27">
+        <v>0.11190479958844</v>
+      </c>
+      <c r="AU27">
+        <v>8.4667409245855405E-2</v>
+      </c>
+      <c r="AV27">
+        <v>5.6885428137994902E-2</v>
+      </c>
+      <c r="AW27">
+        <v>2.88411240954017E-2</v>
+      </c>
+      <c r="AX27">
+        <v>6.0599287326466598E-2</v>
+      </c>
+      <c r="AY27">
+        <v>3.3969340521237901E-2</v>
+      </c>
+      <c r="AZ27">
+        <v>7.71975206459695E-3</v>
+      </c>
+      <c r="BA27">
+        <v>5.2875883544135402E-2</v>
+      </c>
+      <c r="BB27">
+        <v>1.3399996856671001E-2</v>
+      </c>
+      <c r="BC27">
+        <v>1.2707572148912201E-2</v>
+      </c>
+      <c r="BD27">
+        <v>8.5988800383993397E-2</v>
+      </c>
+      <c r="BE27">
+        <v>4.7948023711195498E-2</v>
+      </c>
+      <c r="BF27">
+        <v>2.2946267006140001E-2</v>
+      </c>
+      <c r="BG27">
+        <v>6.5100587940530197E-2</v>
+      </c>
+      <c r="BH27">
+        <v>2.8919491507044801E-2</v>
+      </c>
+      <c r="BI27">
+        <v>5.6868631060965997E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>0.84405517976409705</v>
+      </c>
+      <c r="G28">
+        <v>0.30444927782579501</v>
+      </c>
+      <c r="H28">
+        <v>0.19347257327078801</v>
+      </c>
+      <c r="I28">
+        <v>0.35167707417370098</v>
+      </c>
+      <c r="J28">
+        <v>0.11028305272267</v>
+      </c>
+      <c r="K28">
+        <v>0.29224050860739798</v>
+      </c>
+      <c r="L28">
+        <v>9.5025766679771195E-2</v>
+      </c>
+      <c r="M28">
+        <v>6.8832798125947503E-2</v>
+      </c>
+      <c r="N28">
+        <v>2.1747179707675399E-2</v>
+      </c>
+      <c r="O28">
+        <v>6.7128487989851299E-2</v>
+      </c>
+      <c r="P28">
+        <v>1.9381845284756401E-2</v>
+      </c>
+      <c r="Q28">
+        <v>8.3547390347989706E-2</v>
+      </c>
+      <c r="R28">
+        <v>5.51508498274473E-2</v>
+      </c>
+      <c r="S28">
+        <v>1.9934093487915701E-2</v>
+      </c>
+      <c r="T28">
+        <v>2.3062574867941901E-2</v>
+      </c>
+      <c r="U28">
+        <v>0.100927295920044</v>
+      </c>
+      <c r="V28">
+        <v>1.37748816335285E-2</v>
+      </c>
+      <c r="W28">
+        <v>3.3803706513900897E-2</v>
+      </c>
+      <c r="X28">
+        <v>1.9870515831746999E-2</v>
+      </c>
+      <c r="Y28">
+        <v>4.0744633242611301E-2</v>
+      </c>
+      <c r="Z28">
+        <v>2.44007122697215E-2</v>
+      </c>
+      <c r="AA28">
+        <v>4.6175222246807097E-2</v>
+      </c>
+      <c r="AB28">
+        <v>2.8829279592364799E-2</v>
+      </c>
+      <c r="AC28">
+        <v>7.1346196455688293E-2</v>
+      </c>
+      <c r="AD28">
+        <v>3.3500101974977402E-2</v>
+      </c>
+      <c r="AE28">
+        <v>7.3963510836943594E-2</v>
+      </c>
+      <c r="AF28">
+        <v>3.6542742673785898E-2</v>
+      </c>
+      <c r="AG28">
+        <v>1.1144282148448301E-2</v>
+      </c>
+      <c r="AH28">
+        <v>6.1175842516224398E-2</v>
+      </c>
+      <c r="AI28">
+        <v>8.2463882411889997E-2</v>
+      </c>
+      <c r="AJ28">
+        <v>6.2453581358648799E-2</v>
+      </c>
+      <c r="AK28">
+        <v>1.4720849714501201E-2</v>
+      </c>
+      <c r="AL28">
+        <v>6.3997703007017098E-2</v>
+      </c>
+      <c r="AM28">
+        <v>0.105725897497413</v>
+      </c>
+      <c r="AN28">
+        <v>6.3804488443631194E-2</v>
+      </c>
+      <c r="AO28">
+        <v>3.7717903703137601E-2</v>
+      </c>
+      <c r="AP28">
+        <v>6.5362533654895097E-2</v>
+      </c>
+      <c r="AQ28">
+        <v>4.0427238688019902E-2</v>
+      </c>
+      <c r="AR28">
+        <v>1.3588563432919899E-2</v>
+      </c>
+      <c r="AS28">
+        <v>0.105232591821664</v>
+      </c>
+      <c r="AT28">
+        <v>8.2484416987009895E-2</v>
+      </c>
+      <c r="AU28">
+        <v>3.9340983984062397E-2</v>
+      </c>
+      <c r="AV28">
+        <v>1.3196797266541599E-2</v>
+      </c>
+      <c r="AW28">
+        <v>4.2539525533094903E-2</v>
+      </c>
+      <c r="AX28">
+        <v>1.6964319194402999E-2</v>
+      </c>
+      <c r="AY28">
+        <v>3.7273251093405603E-2</v>
+      </c>
+      <c r="AZ28">
+        <v>8.1063815809198206E-2</v>
+      </c>
+      <c r="BA28">
+        <v>4.08609042402404E-2</v>
+      </c>
+      <c r="BB28">
+        <v>1.60018610059975E-2</v>
+      </c>
+      <c r="BC28">
+        <v>4.4497553451515202E-2</v>
+      </c>
+      <c r="BD28">
+        <v>2.0267318943070801E-2</v>
+      </c>
+      <c r="BE28">
+        <v>3.8592211995100802E-2</v>
+      </c>
+      <c r="BF28">
+        <v>8.0002358393224698E-2</v>
+      </c>
+      <c r="BG28">
+        <v>4.2588583792391402E-2</v>
+      </c>
+      <c r="BH28">
+        <v>1.90347519000773E-2</v>
+      </c>
+      <c r="BI28">
+        <v>2.1834418240248999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29">
+        <v>0.54882283319430403</v>
+      </c>
+      <c r="H29">
+        <v>0.29415727463110602</v>
+      </c>
+      <c r="I29">
+        <v>0.37560339403687198</v>
+      </c>
+      <c r="J29">
+        <v>0.12626312159741299</v>
+      </c>
+      <c r="K29">
+        <v>8.4086416574834705E-2</v>
+      </c>
+      <c r="L29">
+        <v>5.8079141167964803E-2</v>
+      </c>
+      <c r="M29">
+        <v>6.3371065585331302E-2</v>
+      </c>
+      <c r="N29">
+        <v>0.23980317286559399</v>
+      </c>
+      <c r="O29">
+        <v>6.7915017571458694E-2</v>
+      </c>
+      <c r="P29">
+        <v>4.7607012045295098E-2</v>
+      </c>
+      <c r="Q29">
+        <v>1.1007909856830599E-2</v>
+      </c>
+      <c r="R29">
+        <v>4.9567126049309303E-2</v>
+      </c>
+      <c r="S29">
+        <v>1.55382441732344E-2</v>
+      </c>
+      <c r="T29">
+        <v>7.0597953821655901E-2</v>
+      </c>
+      <c r="U29">
+        <v>2.4456102335690601E-2</v>
+      </c>
+      <c r="V29">
+        <v>3.3739423107964503E-2</v>
+      </c>
+      <c r="W29">
+        <v>1.5944792968530502E-2</v>
+      </c>
+      <c r="X29">
+        <v>2.8132599260407901E-2</v>
+      </c>
+      <c r="Y29">
+        <v>5.2269032363463599E-2</v>
+      </c>
+      <c r="Z29">
+        <v>3.9562486741257501E-2</v>
+      </c>
+      <c r="AA29">
+        <v>2.0804861074592701E-2</v>
+      </c>
+      <c r="AB29">
+        <v>5.0356837292663499E-2</v>
+      </c>
+      <c r="AC29">
+        <v>7.1441484775924005E-2</v>
+      </c>
+      <c r="AD29">
+        <v>5.0450135697802302E-2</v>
+      </c>
+      <c r="AE29">
+        <v>3.0714899901714301E-2</v>
+      </c>
+      <c r="AF29">
+        <v>5.6834315364122902E-2</v>
+      </c>
+      <c r="AG29">
+        <v>7.3786820000952297E-2</v>
+      </c>
+      <c r="AH29">
+        <v>5.9173663759314599E-2</v>
+      </c>
+      <c r="AI29">
+        <v>1.2210109447630501E-2</v>
+      </c>
+      <c r="AJ29">
+        <v>6.3507910779070503E-2</v>
+      </c>
+      <c r="AK29">
+        <v>8.2462954315815601E-2</v>
+      </c>
+      <c r="AL29">
+        <v>6.4936390581413705E-2</v>
+      </c>
+      <c r="AM29">
+        <v>1.826273767538E-2</v>
+      </c>
+      <c r="AN29">
+        <v>4.62048803777255E-2</v>
+      </c>
+      <c r="AO29">
+        <v>8.7826537860726403E-2</v>
+      </c>
+      <c r="AP29">
+        <v>4.7489940222724902E-2</v>
+      </c>
+      <c r="AQ29">
+        <v>2.2075720605111E-2</v>
+      </c>
+      <c r="AR29">
+        <v>4.9565925350985703E-2</v>
+      </c>
+      <c r="AS29">
+        <v>9.0212857942606806E-2</v>
+      </c>
+      <c r="AT29">
+        <v>4.9096919460433298E-2</v>
+      </c>
+      <c r="AU29">
+        <v>7.3577228613880205E-2</v>
+      </c>
+      <c r="AV29">
+        <v>5.1203110108910398E-2</v>
+      </c>
+      <c r="AW29">
+        <v>5.6363321856785402E-3</v>
+      </c>
+      <c r="AX29">
+        <v>4.9163335951882603E-2</v>
+      </c>
+      <c r="AY29">
+        <v>7.4191251416778695E-2</v>
+      </c>
+      <c r="AZ29">
+        <v>3.2309241667956297E-2</v>
+      </c>
+      <c r="BA29">
+        <v>9.1866000363174903E-3</v>
+      </c>
+      <c r="BB29">
+        <v>9.4406940331622197E-2</v>
+      </c>
+      <c r="BC29">
+        <v>5.6487367040558602E-2</v>
+      </c>
+      <c r="BD29">
+        <v>3.2923874728237601E-2</v>
+      </c>
+      <c r="BE29">
+        <v>1.50877388898563E-2</v>
+      </c>
+      <c r="BF29">
+        <v>7.7791073282625897E-2</v>
+      </c>
+      <c r="BG29">
+        <v>5.5770888630230997E-2</v>
+      </c>
+      <c r="BH29">
+        <v>1.5444308631974799E-2</v>
+      </c>
+      <c r="BI29">
+        <v>4.1829076235932697E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30">
+        <v>0.50380073319244301</v>
+      </c>
+      <c r="I30">
+        <v>0.22052434417359601</v>
+      </c>
+      <c r="J30">
+        <v>0.55202570304304599</v>
+      </c>
+      <c r="K30">
+        <v>8.76497061340136E-2</v>
+      </c>
+      <c r="L30">
+        <v>0.26886384404195302</v>
+      </c>
+      <c r="M30">
+        <v>6.4798518632644297E-2</v>
+      </c>
+      <c r="N30">
+        <v>4.3921245087833002E-2</v>
+      </c>
+      <c r="O30">
+        <v>2.2925102410226599E-2</v>
+      </c>
+      <c r="P30">
+        <v>3.5871515775479403E-2</v>
+      </c>
+      <c r="Q30">
+        <v>0.204796613313142</v>
+      </c>
+      <c r="R30">
+        <v>4.8297650971948498E-2</v>
+      </c>
+      <c r="S30">
+        <v>3.4014991503528699E-2</v>
+      </c>
+      <c r="T30">
+        <v>2.6047218690283501E-2</v>
+      </c>
+      <c r="U30">
+        <v>3.44375281478854E-2</v>
+      </c>
+      <c r="V30">
+        <v>0.198187577628333</v>
+      </c>
+      <c r="W30">
+        <v>4.4517757629927802E-2</v>
+      </c>
+      <c r="X30">
+        <v>2.98070461854213E-2</v>
+      </c>
+      <c r="Y30">
+        <v>4.63937885034722E-2</v>
+      </c>
+      <c r="Z30">
+        <v>1.2493929041374899E-2</v>
+      </c>
+      <c r="AA30">
+        <v>4.1701130640470499E-2</v>
+      </c>
+      <c r="AB30">
+        <v>6.4521349389820501E-2</v>
+      </c>
+      <c r="AC30">
+        <v>4.56781837011173E-2</v>
+      </c>
+      <c r="AD30">
+        <v>1.2838287071069199E-2</v>
+      </c>
+      <c r="AE30">
+        <v>4.9475907819668902E-2</v>
+      </c>
+      <c r="AF30">
+        <v>6.9128160684300805E-2</v>
+      </c>
+      <c r="AG30">
+        <v>3.2119839873393202E-2</v>
+      </c>
+      <c r="AH30">
+        <v>5.0154130067235798E-3</v>
+      </c>
+      <c r="AI30">
+        <v>8.7726882869600203E-2</v>
+      </c>
+      <c r="AJ30">
+        <v>6.1618737685563703E-2</v>
+      </c>
+      <c r="AK30">
+        <v>4.0353221978418598E-2</v>
+      </c>
+      <c r="AL30">
+        <v>2.06015396897304E-2</v>
+      </c>
+      <c r="AM30">
+        <v>8.4097466213122904E-2</v>
+      </c>
+      <c r="AN30">
+        <v>4.60162847159932E-2</v>
+      </c>
+      <c r="AO30">
+        <v>2.0530557410022202E-2</v>
+      </c>
+      <c r="AP30">
+        <v>4.9307541350789401E-2</v>
+      </c>
+      <c r="AQ30">
+        <v>7.2341739530502297E-2</v>
+      </c>
+      <c r="AR30">
+        <v>5.0899671767829197E-2</v>
+      </c>
+      <c r="AS30">
+        <v>7.5949062110782697E-3</v>
+      </c>
+      <c r="AT30">
+        <v>9.3667813554235105E-2</v>
+      </c>
+      <c r="AU30">
+        <v>5.5682277049262402E-2</v>
+      </c>
+      <c r="AV30">
+        <v>3.1448641360834098E-2</v>
+      </c>
+      <c r="AW30">
+        <v>2.7481728145244199E-2</v>
+      </c>
+      <c r="AX30">
+        <v>7.9633728924685801E-2</v>
+      </c>
+      <c r="AY30">
+        <v>3.6504678874422603E-2</v>
+      </c>
+      <c r="AZ30">
+        <v>1.2858265217549601E-2</v>
+      </c>
+      <c r="BA30">
+        <v>9.9764518373015199E-2</v>
+      </c>
+      <c r="BB30">
+        <v>6.2727451484975202E-2</v>
+      </c>
+      <c r="BC30">
+        <v>1.6812107304698801E-2</v>
+      </c>
+      <c r="BD30">
+        <v>1.5773339923837199E-2</v>
+      </c>
+      <c r="BE30">
+        <v>8.4773498756287799E-2</v>
+      </c>
+      <c r="BF30">
+        <v>4.4441882789294798E-2</v>
+      </c>
+      <c r="BG30">
+        <v>8.7535847596590301E-3</v>
+      </c>
+      <c r="BH30">
+        <v>8.8489779657919598E-2</v>
+      </c>
+      <c r="BI30">
+        <v>6.81543380100295E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31">
+        <v>0.49348168644652102</v>
+      </c>
+      <c r="J31">
+        <v>0.59120515515738603</v>
+      </c>
+      <c r="K31">
+        <v>0.240883762979751</v>
+      </c>
+      <c r="L31">
+        <v>4.6520120718807997E-2</v>
+      </c>
+      <c r="M31">
+        <v>0.26623922242068299</v>
+      </c>
+      <c r="N31">
+        <v>2.571204131645E-2</v>
+      </c>
+      <c r="O31">
+        <v>0.176086146699552</v>
+      </c>
+      <c r="P31">
+        <v>6.1625112491243202E-2</v>
+      </c>
+      <c r="Q31">
+        <v>0.14477846122982399</v>
+      </c>
+      <c r="R31">
+        <v>4.7801779164079003E-2</v>
+      </c>
+      <c r="S31">
+        <v>0.14467261044118099</v>
+      </c>
+      <c r="T31">
+        <v>2.54494207367526E-2</v>
+      </c>
+      <c r="U31">
+        <v>3.96142358904613E-2</v>
+      </c>
+      <c r="V31">
+        <v>2.6423146803860799E-2</v>
+      </c>
+      <c r="W31">
+        <v>4.1547706213157801E-2</v>
+      </c>
+      <c r="X31">
+        <v>2.0434407593620099E-2</v>
+      </c>
+      <c r="Y31">
+        <v>3.6784138584629901E-2</v>
+      </c>
+      <c r="Z31">
+        <v>5.5259130338786301E-2</v>
+      </c>
+      <c r="AA31">
+        <v>1.6174083476824499E-2</v>
+      </c>
+      <c r="AB31">
+        <v>5.8237303115946097E-2</v>
+      </c>
+      <c r="AC31">
+        <v>1.6199002694269E-2</v>
+      </c>
+      <c r="AD31">
+        <v>4.6450642327213597E-2</v>
+      </c>
+      <c r="AE31">
+        <v>6.7558572751936399E-2</v>
+      </c>
+      <c r="AF31">
+        <v>2.4237445510445502E-2</v>
+      </c>
+      <c r="AG31">
+        <v>1.08916122161063E-2</v>
+      </c>
+      <c r="AH31">
+        <v>8.4827744870643998E-2</v>
+      </c>
+      <c r="AI31">
+        <v>5.9177196344402903E-2</v>
+      </c>
+      <c r="AJ31">
+        <v>2.8958494563573901E-3</v>
+      </c>
+      <c r="AK31">
+        <v>9.2306199017814505E-2</v>
+      </c>
+      <c r="AL31">
+        <v>8.2479480138453604E-2</v>
+      </c>
+      <c r="AM31">
+        <v>4.1954542416233899E-2</v>
+      </c>
+      <c r="AN31">
+        <v>2.9442889383873301E-2</v>
+      </c>
+      <c r="AO31">
+        <v>8.7854833977695099E-2</v>
+      </c>
+      <c r="AP31">
+        <v>4.7318577621438297E-2</v>
+      </c>
+      <c r="AQ31">
+        <v>2.0784409549890599E-2</v>
+      </c>
+      <c r="AR31">
+        <v>5.2528110181796699E-2</v>
+      </c>
+      <c r="AS31">
+        <v>7.5548684828285098E-2</v>
+      </c>
+      <c r="AT31">
+        <v>2.5664003259612302E-2</v>
+      </c>
+      <c r="AU31">
+        <v>5.6896208330214797E-2</v>
+      </c>
+      <c r="AV31">
+        <v>7.9858804047214002E-2</v>
+      </c>
+      <c r="AW31">
+        <v>3.0938950888637899E-2</v>
+      </c>
+      <c r="AX31">
+        <v>8.2165799260839306E-2</v>
+      </c>
+      <c r="AY31">
+        <v>3.6854970886394403E-2</v>
+      </c>
+      <c r="AZ31">
+        <v>6.26617283673961E-2</v>
+      </c>
+      <c r="BA31">
+        <v>8.5830400723470507E-2</v>
+      </c>
+      <c r="BB31">
+        <v>4.1284082663025599E-2</v>
+      </c>
+      <c r="BC31">
+        <v>2.2534404143884999E-2</v>
+      </c>
+      <c r="BD31">
+        <v>8.9434784504620904E-2</v>
+      </c>
+      <c r="BE31">
+        <v>4.5875132737655998E-2</v>
+      </c>
+      <c r="BF31">
+        <v>2.1498298669952801E-2</v>
+      </c>
+      <c r="BG31">
+        <v>0.108742162461791</v>
+      </c>
+      <c r="BH31">
+        <v>7.2784633279179001E-2</v>
+      </c>
+      <c r="BI31">
+        <v>2.5674926108358701E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32">
+        <v>0.50848204863223001</v>
+      </c>
+      <c r="K32">
+        <v>0.31842796761387698</v>
+      </c>
+      <c r="L32">
+        <v>0.25358861979483499</v>
+      </c>
+      <c r="M32">
+        <v>0.29098212356360398</v>
+      </c>
+      <c r="N32">
+        <v>0.21167386958367901</v>
+      </c>
+      <c r="O32">
+        <v>0.20092986633826301</v>
+      </c>
+      <c r="P32">
+        <v>0.18782357893863399</v>
+      </c>
+      <c r="Q32">
+        <v>0.143701075933412</v>
+      </c>
+      <c r="R32">
+        <v>0.18039263197942601</v>
+      </c>
+      <c r="S32">
+        <v>7.2857470912094699E-2</v>
+      </c>
+      <c r="T32">
+        <v>9.2158592642613196E-2</v>
+      </c>
+      <c r="U32">
+        <v>5.3527835340683103E-2</v>
+      </c>
+      <c r="V32">
+        <v>0.116632093391699</v>
+      </c>
+      <c r="W32">
+        <v>6.0355409000140602E-2</v>
+      </c>
+      <c r="X32">
+        <v>6.5318867688871102E-2</v>
+      </c>
+      <c r="Y32">
+        <v>8.8891770765661002E-2</v>
+      </c>
+      <c r="Z32">
+        <v>5.6009160879387697E-2</v>
+      </c>
+      <c r="AA32">
+        <v>9.6902818927600103E-3</v>
+      </c>
+      <c r="AB32">
+        <v>3.6828265745629703E-2</v>
+      </c>
+      <c r="AC32">
+        <v>6.6064430637152699E-2</v>
+      </c>
+      <c r="AD32">
+        <v>2.53722156912665E-3</v>
+      </c>
+      <c r="AE32">
+        <v>5.0836814725132198E-2</v>
+      </c>
+      <c r="AF32">
+        <v>7.4429752482447403E-2</v>
+      </c>
+      <c r="AG32">
+        <v>1.1538937719010199E-2</v>
+      </c>
+      <c r="AH32">
+        <v>5.7582622632037297E-2</v>
+      </c>
+      <c r="AI32">
+        <v>2.6381013189275399E-2</v>
+      </c>
+      <c r="AJ32">
+        <v>5.92547718776604E-2</v>
+      </c>
+      <c r="AK32">
+        <v>8.3380730703703498E-2</v>
+      </c>
+      <c r="AL32">
+        <v>3.5783257321165399E-2</v>
+      </c>
+      <c r="AM32">
+        <v>6.0085754117932197E-2</v>
+      </c>
+      <c r="AN32">
+        <v>8.8919017247104395E-2</v>
+      </c>
+      <c r="AO32">
+        <v>4.1146054198767698E-2</v>
+      </c>
+      <c r="AP32">
+        <v>7.3920481730896395E-2</v>
+      </c>
+      <c r="AQ32">
+        <v>9.3861697503365898E-2</v>
+      </c>
+      <c r="AR32">
+        <v>4.6383169267774998E-2</v>
+      </c>
+      <c r="AS32">
+        <v>7.8245948507483606E-2</v>
+      </c>
+      <c r="AT32">
+        <v>2.0240508197587201E-2</v>
+      </c>
+      <c r="AU32">
+        <v>5.1465442283097698E-2</v>
+      </c>
+      <c r="AV32">
+        <v>8.2336237155586203E-2</v>
+      </c>
+      <c r="AW32">
+        <v>5.9010736300673897E-2</v>
+      </c>
+      <c r="AX32">
+        <v>1.7299080627527701E-2</v>
+      </c>
+      <c r="AY32">
+        <v>0.104344692496077</v>
+      </c>
+      <c r="AZ32">
+        <v>6.3081547278281497E-2</v>
+      </c>
+      <c r="BA32">
+        <v>1.16931516174176E-2</v>
+      </c>
+      <c r="BB32">
+        <v>0.107818333971064</v>
+      </c>
+      <c r="BC32">
+        <v>6.7125828740547899E-2</v>
+      </c>
+      <c r="BD32">
+        <v>9.2473227340605701E-2</v>
+      </c>
+      <c r="BE32">
+        <v>4.4500755486742503E-2</v>
+      </c>
+      <c r="BF32">
+        <v>7.1140085209357301E-2</v>
+      </c>
+      <c r="BG32">
+        <v>9.5773758074266302E-2</v>
+      </c>
+      <c r="BH32">
+        <v>4.8694487924442399E-2</v>
+      </c>
+      <c r="BI32">
+        <v>2.3052036119538401E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33">
+        <v>0.56361665437650299</v>
+      </c>
+      <c r="L33">
+        <v>0.345658444148285</v>
+      </c>
+      <c r="M33">
+        <v>9.1525060305521294E-2</v>
+      </c>
+      <c r="N33">
+        <v>0.24606499352349101</v>
+      </c>
+      <c r="O33">
+        <v>0.226865008168608</v>
+      </c>
+      <c r="P33">
+        <v>0.20971036239322399</v>
+      </c>
+      <c r="Q33">
+        <v>7.4261253416248493E-2</v>
+      </c>
+      <c r="R33">
+        <v>0.21808632329461999</v>
+      </c>
+      <c r="S33">
+        <v>7.1607300820813499E-2</v>
+      </c>
+      <c r="T33">
+        <v>8.7595792498979003E-2</v>
+      </c>
+      <c r="U33">
+        <v>0.18988447553145901</v>
+      </c>
+      <c r="V33">
+        <v>8.6683889640894296E-2</v>
+      </c>
+      <c r="W33">
+        <v>5.4953792155864198E-2</v>
+      </c>
+      <c r="X33">
+        <v>6.3578890560959098E-2</v>
+      </c>
+      <c r="Y33">
+        <v>9.6502842755628093E-2</v>
+      </c>
+      <c r="Z33">
+        <v>8.1482058405643598E-2</v>
+      </c>
+      <c r="AA33">
+        <v>7.2355053009483306E-2</v>
+      </c>
+      <c r="AB33">
+        <v>7.2250813672023795E-2</v>
+      </c>
+      <c r="AC33">
+        <v>4.0794740019208499E-2</v>
+      </c>
+      <c r="AD33">
+        <v>7.9113566217860296E-2</v>
+      </c>
+      <c r="AE33">
+        <v>9.1574515604315496E-2</v>
+      </c>
+      <c r="AF33">
+        <v>4.82025331945517E-2</v>
+      </c>
+      <c r="AG33">
+        <v>9.9234511398982803E-2</v>
+      </c>
+      <c r="AH33">
+        <v>9.9401905766693097E-2</v>
+      </c>
+      <c r="AI33">
+        <v>5.4628785796582299E-2</v>
+      </c>
+      <c r="AJ33">
+        <v>8.7961238266519207E-2</v>
+      </c>
+      <c r="AK33">
+        <v>2.1384584778840001E-2</v>
+      </c>
+      <c r="AL33">
+        <v>6.0351812654480301E-2</v>
+      </c>
+      <c r="AM33">
+        <v>9.3145794826720502E-2</v>
+      </c>
+      <c r="AN33">
+        <v>2.7382235739175101E-2</v>
+      </c>
+      <c r="AO33">
+        <v>0.110884632079565</v>
+      </c>
+      <c r="AP33">
+        <v>9.7715410093391006E-2</v>
+      </c>
+      <c r="AQ33">
+        <v>3.33707066648758E-2</v>
+      </c>
+      <c r="AR33">
+        <v>7.81659721567875E-2</v>
+      </c>
+      <c r="AS33">
+        <v>1.29885455571443E-2</v>
+      </c>
+      <c r="AT33">
+        <v>3.9174373542267701E-2</v>
+      </c>
+      <c r="AU33">
+        <v>8.2093459363934695E-2</v>
+      </c>
+      <c r="AV33">
+        <v>1.12437826064431E-2</v>
+      </c>
+      <c r="AW33">
+        <v>0.12225270969813901</v>
+      </c>
+      <c r="AX33">
+        <v>8.5840433622703993E-2</v>
+      </c>
+      <c r="AY33">
+        <v>1.3958284414535E-2</v>
+      </c>
+      <c r="AZ33">
+        <v>6.2194234816412099E-2</v>
+      </c>
+      <c r="BA33">
+        <v>8.9449355747093506E-2</v>
+      </c>
+      <c r="BB33">
+        <v>0.11335701558736901</v>
+      </c>
+      <c r="BC33">
+        <v>6.6082242711715602E-2</v>
+      </c>
+      <c r="BD33">
+        <v>2.1471201895964701E-2</v>
+      </c>
+      <c r="BE33">
+        <v>0.116429259814922</v>
+      </c>
+      <c r="BF33">
+        <v>6.9955217679421894E-2</v>
+      </c>
+      <c r="BG33">
+        <v>9.9591262997243205E-2</v>
+      </c>
+      <c r="BH33">
+        <v>4.5034232703787203E-2</v>
+      </c>
+      <c r="BI33">
+        <v>3.38722017528401E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34">
+        <v>0.66973877121577796</v>
+      </c>
+      <c r="M34">
+        <v>0.40071543018137001</v>
+      </c>
+      <c r="N34">
+        <v>0.31274501595494197</v>
+      </c>
+      <c r="O34">
+        <v>0.26679075876353803</v>
+      </c>
+      <c r="P34">
+        <v>0.24296098078036299</v>
+      </c>
+      <c r="Q34">
+        <v>0.229406068334154</v>
+      </c>
+      <c r="R34">
+        <v>0.18721728872578899</v>
+      </c>
+      <c r="S34">
+        <v>0.21467387302222399</v>
+      </c>
+      <c r="T34">
+        <v>0.10603398118681</v>
+      </c>
+      <c r="U34">
+        <v>0.101537358983113</v>
+      </c>
+      <c r="V34">
+        <v>9.3610068399910304E-2</v>
+      </c>
+      <c r="W34">
+        <v>5.1384797449208701E-2</v>
+      </c>
+      <c r="X34">
+        <v>8.9926923325026095E-2</v>
+      </c>
+      <c r="Y34">
+        <v>9.5877024918152295E-2</v>
+      </c>
+      <c r="Z34">
+        <v>0.40975505930679701</v>
+      </c>
+      <c r="AA34">
+        <v>1.95194815756859E-2</v>
+      </c>
+      <c r="AB34">
+        <v>8.8835367992884398E-2</v>
+      </c>
+      <c r="AC34">
+        <v>0.113825533803419</v>
+      </c>
+      <c r="AD34">
+        <v>1.5640123321333702E-2</v>
+      </c>
+      <c r="AE34">
+        <v>8.8460273265947104E-2</v>
+      </c>
+      <c r="AF34">
+        <v>0.117836211600685</v>
+      </c>
+      <c r="AG34">
+        <v>2.2813415454806699E-2</v>
+      </c>
+      <c r="AH34">
+        <v>9.2859671552046094E-2</v>
+      </c>
+      <c r="AI34">
+        <v>3.7556655866037E-2</v>
+      </c>
+      <c r="AJ34">
+        <v>0.122283661417719</v>
+      </c>
+      <c r="AK34">
+        <v>9.6734627930342904E-2</v>
+      </c>
+      <c r="AL34">
+        <v>2.3544091897451502E-2</v>
+      </c>
+      <c r="AM34">
+        <v>6.6869571540680697E-2</v>
+      </c>
+      <c r="AN34">
+        <v>0.100254101306494</v>
+      </c>
+      <c r="AO34">
+        <v>0.120401155665341</v>
+      </c>
+      <c r="AP34">
+        <v>7.1212297118594697E-2</v>
+      </c>
+      <c r="AQ34">
+        <v>0.106099158813799</v>
+      </c>
+      <c r="AR34">
+        <v>0.10741080790325</v>
+      </c>
+      <c r="AS34">
+        <v>5.1364683873520098E-3</v>
+      </c>
+      <c r="AT34">
+        <v>7.9267475349388203E-2</v>
+      </c>
+      <c r="AU34">
+        <v>4.3035734957800997E-2</v>
+      </c>
+      <c r="AV34">
+        <v>0.131064378984772</v>
+      </c>
+      <c r="AW34">
+        <v>8.2991013993913898E-2</v>
+      </c>
+      <c r="AX34">
+        <v>3.1867829456066497E-2</v>
+      </c>
+      <c r="AY34">
+        <v>5.2867239836032698E-2</v>
+      </c>
+      <c r="AZ34">
+        <v>8.6605294100699504E-2</v>
+      </c>
+      <c r="BA34">
+        <v>0.118510011620033</v>
+      </c>
+      <c r="BB34">
+        <v>1.6680611067663699E-2</v>
+      </c>
+      <c r="BC34">
+        <v>6.0439462107184302E-2</v>
+      </c>
+      <c r="BD34">
+        <v>9.3426298426525695E-2</v>
+      </c>
+      <c r="BE34">
+        <v>0.12385453632134</v>
+      </c>
+      <c r="BF34">
+        <v>6.4616765837853501E-2</v>
+      </c>
+      <c r="BG34">
+        <v>9.6740299065893598E-2</v>
+      </c>
+      <c r="BH34">
+        <v>0.12638336273804901</v>
+      </c>
+      <c r="BI34">
+        <v>6.8758126637397804E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35">
+        <v>0.49822273811819801</v>
+      </c>
+      <c r="O35">
+        <v>0.36469952577686998</v>
+      </c>
+      <c r="P35">
+        <v>0.311764167674138</v>
+      </c>
+      <c r="Q35">
+        <v>0.27158905843868197</v>
+      </c>
+      <c r="R35">
+        <v>0.143203874613688</v>
+      </c>
+      <c r="S35">
+        <v>0.244547755671496</v>
+      </c>
+      <c r="T35">
+        <v>0.23579698612553199</v>
+      </c>
+      <c r="U35">
+        <v>7.7855285582335093E-2</v>
+      </c>
+      <c r="V35">
+        <v>0.22680074406777301</v>
+      </c>
+      <c r="W35">
+        <v>0.33432781922917798</v>
+      </c>
+      <c r="X35">
+        <v>0.484912897518123</v>
+      </c>
+      <c r="Y35">
+        <v>8.6947111175090797E-2</v>
+      </c>
+      <c r="Z35">
+        <v>0.21046883483058801</v>
+      </c>
+      <c r="AA35">
+        <v>0.142447922900659</v>
+      </c>
+      <c r="AB35">
+        <v>8.3847132160667498E-2</v>
+      </c>
+      <c r="AC35">
+        <v>0.12432125348329499</v>
+      </c>
+      <c r="AD35">
+        <v>1.22669127266335E-2</v>
+      </c>
+      <c r="AE35">
+        <v>0.15014429152821299</v>
+      </c>
+      <c r="AF35">
+        <v>9.35431471001993E-2</v>
+      </c>
+      <c r="AG35">
+        <v>0.25786575194820499</v>
+      </c>
+      <c r="AH35">
+        <v>2.4865662896776001E-2</v>
+      </c>
+      <c r="AI35">
+        <v>9.4374982855503206E-2</v>
+      </c>
+      <c r="AJ35">
+        <v>0.13392699752256501</v>
+      </c>
+      <c r="AK35">
+        <v>3.4552004164935202E-2</v>
+      </c>
+      <c r="AL35">
+        <v>0.10874132025914</v>
+      </c>
+      <c r="AM35">
+        <v>0.13595387706487899</v>
+      </c>
+      <c r="AN35">
+        <v>4.2864093775445901E-2</v>
+      </c>
+      <c r="AO35">
+        <v>4.88252102227998E-2</v>
+      </c>
+      <c r="AP35">
+        <v>0.20597036369545099</v>
+      </c>
+      <c r="AQ35">
+        <v>0.141363052864862</v>
+      </c>
+      <c r="AR35">
+        <v>5.5610276962365701E-2</v>
+      </c>
+      <c r="AS35">
+        <v>0.11749197331899</v>
+      </c>
+      <c r="AT35">
+        <v>2.2615572123232699E-2</v>
+      </c>
+      <c r="AU35">
+        <v>0.152821131787339</v>
+      </c>
+      <c r="AV35">
+        <v>6.6700000897188999E-2</v>
+      </c>
+      <c r="AW35">
+        <v>0.142750038312734</v>
+      </c>
+      <c r="AX35">
+        <v>0.14770406763628099</v>
+      </c>
+      <c r="AY35">
+        <v>7.1990101605076504E-2</v>
+      </c>
+      <c r="AZ35">
+        <v>0.12515579901061899</v>
+      </c>
+      <c r="BA35">
+        <v>3.2547392700990503E-2</v>
+      </c>
+      <c r="BB35">
+        <v>0.152014893787354</v>
+      </c>
+      <c r="BC35">
+        <v>8.1164122272411904E-2</v>
+      </c>
+      <c r="BD35">
+        <v>0.13019922091129901</v>
+      </c>
+      <c r="BE35">
+        <v>4.19664449792784E-2</v>
+      </c>
+      <c r="BF35">
+        <v>0.16624093722347499</v>
+      </c>
+      <c r="BG35">
+        <v>8.94989778465759E-2</v>
+      </c>
+      <c r="BH35">
+        <v>0.13495139060907299</v>
+      </c>
+      <c r="BI35">
+        <v>5.1547887518144903E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36">
+        <v>0.68996978187520697</v>
+      </c>
+      <c r="P36">
+        <v>0.46870106841383002</v>
+      </c>
+      <c r="Q36">
+        <v>0.371565661088266</v>
+      </c>
+      <c r="R36">
+        <v>0.32539541289639401</v>
+      </c>
+      <c r="S36">
+        <v>0.29712830680102897</v>
+      </c>
+      <c r="T36">
+        <v>0.27561048218936302</v>
+      </c>
+      <c r="U36">
+        <v>0.181539197508572</v>
+      </c>
+      <c r="V36">
+        <v>0.25816446233956702</v>
+      </c>
+      <c r="W36">
+        <v>0.35140900768352701</v>
+      </c>
+      <c r="X36">
+        <v>0.243807805313175</v>
+      </c>
+      <c r="Y36">
+        <v>0.175848073790039</v>
+      </c>
+      <c r="Z36">
+        <v>0.224303346338285</v>
+      </c>
+      <c r="AA36">
+        <v>0.16363789315183999</v>
+      </c>
+      <c r="AB36">
+        <v>0.34903233101871001</v>
+      </c>
+      <c r="AC36">
+        <v>0.23622499699156199</v>
+      </c>
+      <c r="AD36">
+        <v>0.19041399382135199</v>
+      </c>
+      <c r="AE36">
+        <v>0.25466551188147801</v>
+      </c>
+      <c r="AF36">
+        <v>9.9894318893348003E-2</v>
+      </c>
+      <c r="AG36">
+        <v>0.171332746195901</v>
+      </c>
+      <c r="AH36">
+        <v>0.17705125363177601</v>
+      </c>
+      <c r="AI36">
+        <v>0.173778915062483</v>
+      </c>
+      <c r="AJ36">
+        <v>0.10798848667884001</v>
+      </c>
+      <c r="AK36">
+        <v>0.16652505616329599</v>
+      </c>
+      <c r="AL36">
+        <v>0.17195122051287301</v>
+      </c>
+      <c r="AM36">
+        <v>0.10912601502270899</v>
+      </c>
+      <c r="AN36">
+        <v>0.114912411298904</v>
+      </c>
+      <c r="AO36">
+        <v>0.16511159659227001</v>
+      </c>
+      <c r="AP36">
+        <v>7.1009719009359998E-2</v>
+      </c>
+      <c r="AQ36">
+        <v>0.116085856782839</v>
+      </c>
+      <c r="AR36">
+        <v>0.13896157898310599</v>
+      </c>
+      <c r="AS36">
+        <v>0.17651467373179699</v>
+      </c>
+      <c r="AT36">
+        <v>3.2702813592985901E-2</v>
+      </c>
+      <c r="AU36">
+        <v>0.12233864221743999</v>
+      </c>
+      <c r="AV36">
+        <v>0.101994211907757</v>
+      </c>
+      <c r="AW36">
+        <v>0.17997709115768101</v>
+      </c>
+      <c r="AX36">
+        <v>0.12398582402357</v>
+      </c>
+      <c r="AY36">
+        <v>0.128083480254579</v>
+      </c>
+      <c r="AZ36">
+        <v>7.0610499836639196E-2</v>
+      </c>
+      <c r="BA36">
+        <v>0.183236272739148</v>
+      </c>
+      <c r="BB36">
+        <v>0.12972004423543201</v>
+      </c>
+      <c r="BC36">
+        <v>0.13344452541416299</v>
+      </c>
+      <c r="BD36">
+        <v>4.4165624007914503E-2</v>
+      </c>
+      <c r="BE36">
+        <v>0.186337743770845</v>
+      </c>
+      <c r="BF36">
+        <v>0.13508604176417699</v>
+      </c>
+      <c r="BG36">
+        <v>0.138505809999072</v>
+      </c>
+      <c r="BH36">
+        <v>2.2729147397266801E-2</v>
+      </c>
+      <c r="BI36">
+        <v>0.18931615545352801</v>
+      </c>
+    </row>
+    <row r="37" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" t="s">
+        <v>23</v>
+      </c>
+      <c r="P37" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q37">
+        <v>0.69656803240691201</v>
+      </c>
+      <c r="R37">
+        <v>0.50639376952179505</v>
+      </c>
+      <c r="S37">
+        <v>0.418638738329842</v>
+      </c>
+      <c r="T37">
+        <v>0.36451536835001902</v>
+      </c>
+      <c r="U37">
+        <v>0.33125171299221401</v>
+      </c>
+      <c r="V37">
+        <v>0.30923373117280301</v>
+      </c>
+      <c r="W37">
+        <v>0.299475180849816</v>
+      </c>
+      <c r="X37">
+        <v>0.28668938342090799</v>
+      </c>
+      <c r="Y37">
+        <v>0.45489462408046</v>
+      </c>
+      <c r="Z37">
+        <v>0.44132854987894798</v>
+      </c>
+      <c r="AA37">
+        <v>0.33432065197437999</v>
+      </c>
+      <c r="AB37">
+        <v>0.38385702978201303</v>
+      </c>
+      <c r="AC37">
+        <v>0.26789146365792199</v>
+      </c>
+      <c r="AD37">
+        <v>0.213711379544302</v>
+      </c>
+      <c r="AE37">
+        <v>0.15497491888351</v>
+      </c>
+      <c r="AF37">
+        <v>0.28747009656989397</v>
+      </c>
+      <c r="AG37">
+        <v>0.12998947606806699</v>
+      </c>
+      <c r="AH37">
+        <v>0.19704019495325101</v>
+      </c>
+      <c r="AI37">
+        <v>0.249775231785896</v>
+      </c>
+      <c r="AJ37">
+        <v>0.25255763301989997</v>
+      </c>
+      <c r="AK37">
+        <v>4.05739725574615E-2</v>
+      </c>
+      <c r="AL37">
+        <v>0.189505706863244</v>
+      </c>
+      <c r="AM37">
+        <v>0.23266590323151301</v>
+      </c>
+      <c r="AN37">
+        <v>0.20931548501490499</v>
+      </c>
+      <c r="AO37">
+        <v>1.88102021536278E-2</v>
+      </c>
+      <c r="AP37">
+        <v>0.186269965293788</v>
+      </c>
+      <c r="AQ37">
+        <v>0.223549294251595</v>
+      </c>
+      <c r="AR37">
+        <v>0.211528957080164</v>
+      </c>
+      <c r="AS37">
+        <v>5.3426332183246099E-2</v>
+      </c>
+      <c r="AT37">
+        <v>0.18532063109323099</v>
+      </c>
+      <c r="AU37">
+        <v>0.218589867118966</v>
+      </c>
+      <c r="AV37">
+        <v>0.21386318432047099</v>
+      </c>
+      <c r="AW37">
+        <v>0.18235495181830899</v>
+      </c>
+      <c r="AX37">
+        <v>0.18569807546091399</v>
+      </c>
+      <c r="AY37">
+        <v>3.03878938206044E-2</v>
+      </c>
+      <c r="AZ37">
+        <v>0.216226656833957</v>
+      </c>
+      <c r="BA37">
+        <v>9.63068234645688E-2</v>
+      </c>
+      <c r="BB37">
+        <v>0.18688707832205201</v>
+      </c>
+      <c r="BC37">
+        <v>3.6310408609620697E-2</v>
+      </c>
+      <c r="BD37">
+        <v>0.21857542043706399</v>
+      </c>
+      <c r="BE37">
+        <v>0.11045815566238</v>
+      </c>
+      <c r="BF37">
+        <v>0.18859199760718201</v>
+      </c>
+      <c r="BG37">
+        <v>5.1522330544421999E-2</v>
+      </c>
+      <c r="BH37">
+        <v>0.21718536947765399</v>
+      </c>
+      <c r="BI37">
+        <v>0.121974608550859</v>
+      </c>
+    </row>
+    <row r="38" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" t="s">
+        <v>23</v>
+      </c>
+      <c r="P38" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" t="s">
+        <v>23</v>
+      </c>
+      <c r="T38">
+        <v>0.58506683630259504</v>
+      </c>
+      <c r="U38">
+        <v>0.51203307055963898</v>
+      </c>
+      <c r="V38">
+        <v>0.44337050578557102</v>
+      </c>
+      <c r="W38">
+        <v>0.40394122567724799</v>
+      </c>
+      <c r="X38">
+        <v>0.37277180959308598</v>
+      </c>
+      <c r="Y38">
+        <v>0.35036474987635502</v>
+      </c>
+      <c r="Z38">
+        <v>0.33489992578559302</v>
+      </c>
+      <c r="AA38">
+        <v>0.34796863988003501</v>
+      </c>
+      <c r="AB38">
+        <v>0.42529846696414397</v>
+      </c>
+      <c r="AC38">
+        <v>0.65925428615200299</v>
+      </c>
+      <c r="AD38">
+        <v>0.65770634629042601</v>
+      </c>
+      <c r="AE38">
+        <v>8.9052372690261505E-2</v>
+      </c>
+      <c r="AF38">
+        <v>0.324182217628326</v>
+      </c>
+      <c r="AG38">
+        <v>0.38630393824000098</v>
+      </c>
+      <c r="AH38">
+        <v>0.38571623341057198</v>
+      </c>
+      <c r="AI38">
+        <v>0.136878743009893</v>
+      </c>
+      <c r="AJ38">
+        <v>0.28502929369735502</v>
+      </c>
+      <c r="AK38">
+        <v>7.5933540385977494E-2</v>
+      </c>
+      <c r="AL38">
+        <v>0.32377936523087603</v>
+      </c>
+      <c r="AM38">
+        <v>0.16243570330264101</v>
+      </c>
+      <c r="AN38">
+        <v>0.26511604125091798</v>
+      </c>
+      <c r="AO38">
+        <v>4.6827310411793097E-2</v>
+      </c>
+      <c r="AP38">
+        <v>0.29649744472056699</v>
+      </c>
+      <c r="AQ38">
+        <v>0.17428593125316699</v>
+      </c>
+      <c r="AR38">
+        <v>0.25397156860533299</v>
+      </c>
+      <c r="AS38">
+        <v>6.9217405538597995E-2</v>
+      </c>
+      <c r="AT38">
+        <v>0.28159210564793802</v>
+      </c>
+      <c r="AU38">
+        <v>0.181426030139275</v>
+      </c>
+      <c r="AV38">
+        <v>0.24748957779212</v>
+      </c>
+      <c r="AW38">
+        <v>0.45683668567300001</v>
+      </c>
+      <c r="AX38">
+        <v>0.27272197279716198</v>
+      </c>
+      <c r="AY38">
+        <v>0.186709727570296</v>
+      </c>
+      <c r="AZ38">
+        <v>0.19219376397980201</v>
+      </c>
+      <c r="BA38">
+        <v>0.34699063628787802</v>
+      </c>
+      <c r="BB38">
+        <v>0.26731751233004403</v>
+      </c>
+      <c r="BC38">
+        <v>0.191205664747746</v>
+      </c>
+      <c r="BD38">
+        <v>0.19588250296635301</v>
+      </c>
+      <c r="BE38">
+        <v>0.25643820278576501</v>
+      </c>
+      <c r="BF38">
+        <v>0.26403466172475498</v>
+      </c>
+      <c r="BG38">
+        <v>9.34916633321837E-2</v>
+      </c>
+      <c r="BH38">
+        <v>0.199367282762454</v>
+      </c>
+      <c r="BI38">
+        <v>0.243082882664409</v>
+      </c>
+    </row>
+    <row r="39" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" t="s">
+        <v>23</v>
+      </c>
+      <c r="S39" t="s">
+        <v>23</v>
+      </c>
+      <c r="T39" t="s">
+        <v>23</v>
+      </c>
+      <c r="U39" t="s">
+        <v>23</v>
+      </c>
+      <c r="V39" t="s">
+        <v>23</v>
+      </c>
+      <c r="W39">
+        <v>0.72076292584555401</v>
+      </c>
+      <c r="X39">
+        <v>0.60965501407223399</v>
+      </c>
+      <c r="Y39">
+        <v>0.53741069081804105</v>
+      </c>
+      <c r="Z39">
+        <v>0.48619132985136099</v>
+      </c>
+      <c r="AA39">
+        <v>0.45273398584177799</v>
+      </c>
+      <c r="AB39">
+        <v>0.42918895086320102</v>
+      </c>
+      <c r="AC39">
+        <v>0.408642720277405</v>
+      </c>
+      <c r="AD39">
+        <v>0.38789872238171103</v>
+      </c>
+      <c r="AE39">
+        <v>4.3671392098126802E-2</v>
+      </c>
+      <c r="AF39">
+        <v>0.59736388702740695</v>
+      </c>
+      <c r="AG39">
+        <v>0.59467966489021995</v>
+      </c>
+      <c r="AH39">
+        <v>0.43995417691580702</v>
+      </c>
+      <c r="AI39">
+        <v>0.163911732026711</v>
+      </c>
+      <c r="AJ39">
+        <v>0.50539043979430998</v>
+      </c>
+      <c r="AK39">
+        <v>0.41616285594320002</v>
+      </c>
+      <c r="AL39">
+        <v>0.373479109179358</v>
+      </c>
+      <c r="AM39">
+        <v>0.20055876949212401</v>
+      </c>
+      <c r="AN39">
+        <v>0.40080975883422598</v>
+      </c>
+      <c r="AO39">
+        <v>0.35092622138141799</v>
+      </c>
+      <c r="AP39">
+        <v>0.34217232689294802</v>
+      </c>
+      <c r="AQ39">
+        <v>0.51275120216387704</v>
+      </c>
+      <c r="AR39">
+        <v>0.36237958469964499</v>
+      </c>
+      <c r="AS39">
+        <v>0.31919991966280398</v>
+      </c>
+      <c r="AT39">
+        <v>0.32202848183146698</v>
+      </c>
+      <c r="AU39">
+        <v>0.53011006512459002</v>
+      </c>
+      <c r="AV39">
+        <v>0.34217722550406898</v>
+      </c>
+      <c r="AW39">
+        <v>0.33707013262839802</v>
+      </c>
+      <c r="AX39">
+        <v>0.30415986025839298</v>
+      </c>
+      <c r="AY39">
+        <v>0.374686138954273</v>
+      </c>
+      <c r="AZ39">
+        <v>0.363555995460833</v>
+      </c>
+      <c r="BA39">
+        <v>0.33067274069945601</v>
+      </c>
+      <c r="BB39">
+        <v>0.29341622810585999</v>
+      </c>
+      <c r="BC39">
+        <v>0.296072492007669</v>
+      </c>
+      <c r="BD39">
+        <v>0.23023321203007999</v>
+      </c>
+      <c r="BE39">
+        <v>0.32321596500743999</v>
+      </c>
+      <c r="BF39">
+        <v>1.8718365989552999E-2</v>
+      </c>
+      <c r="BG39">
+        <v>0.28946406120614698</v>
+      </c>
+      <c r="BH39">
+        <v>0.129830813480942</v>
+      </c>
+      <c r="BI39">
+        <v>0.32530082482601103</v>
+      </c>
+    </row>
+    <row r="40" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" t="s">
+        <v>23</v>
+      </c>
+      <c r="P40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" t="s">
+        <v>23</v>
+      </c>
+      <c r="S40" t="s">
+        <v>23</v>
+      </c>
+      <c r="T40" t="s">
+        <v>23</v>
+      </c>
+      <c r="U40" t="s">
+        <v>23</v>
+      </c>
+      <c r="V40" t="s">
+        <v>23</v>
+      </c>
+      <c r="W40" t="s">
+        <v>23</v>
+      </c>
+      <c r="X40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC40">
+        <v>0.673694332259408</v>
+      </c>
+      <c r="AD40">
+        <v>0.61619543292295598</v>
+      </c>
+      <c r="AE40">
+        <v>0.57697719967000305</v>
+      </c>
+      <c r="AF40">
+        <v>0.54525880747846101</v>
+      </c>
+      <c r="AG40">
+        <v>0.704905166186655</v>
+      </c>
+      <c r="AH40">
+        <v>0.50099305434821395</v>
+      </c>
+      <c r="AI40">
+        <v>0.48263788663572998</v>
+      </c>
+      <c r="AJ40">
+        <v>0.46606420277437799</v>
+      </c>
+      <c r="AK40">
+        <v>0.51739890285900603</v>
+      </c>
+      <c r="AL40">
+        <v>0.65518567191472099</v>
+      </c>
+      <c r="AM40">
+        <v>0.43986147698684203</v>
+      </c>
+      <c r="AN40">
+        <v>0.488242991191422</v>
+      </c>
+      <c r="AO40">
+        <v>0.42385098451769598</v>
+      </c>
+      <c r="AP40">
+        <v>0.43954158531301601</v>
+      </c>
+      <c r="AQ40">
+        <v>0.54639914735777895</v>
+      </c>
+      <c r="AR40">
+        <v>0.54441147647333499</v>
+      </c>
+      <c r="AS40">
+        <v>0.69733889058369303</v>
+      </c>
+      <c r="AT40">
+        <v>0.39988375764954498</v>
+      </c>
+      <c r="AU40">
+        <v>0.37114435947451002</v>
+      </c>
+      <c r="AV40">
+        <v>0.457909157100235</v>
+      </c>
+      <c r="AW40">
+        <v>0.44362874826223198</v>
+      </c>
+      <c r="AX40">
+        <v>0.42053583142704998</v>
+      </c>
+      <c r="AY40">
+        <v>0.42213666182236798</v>
+      </c>
+      <c r="AZ40">
+        <v>0.419895835914737</v>
+      </c>
+      <c r="BA40">
+        <v>0.419592122838923</v>
+      </c>
+      <c r="BB40">
+        <v>0.19267139674429501</v>
+      </c>
+      <c r="BC40">
+        <v>0.466667709124307</v>
+      </c>
+      <c r="BD40">
+        <v>0.212321296226094</v>
+      </c>
+      <c r="BE40">
+        <v>0.39848808250483397</v>
+      </c>
+      <c r="BF40">
+        <v>0.39908959962541202</v>
+      </c>
+      <c r="BG40">
+        <v>9.0994286986352105E-2</v>
+      </c>
+      <c r="BH40">
+        <v>0.42929258922778601</v>
+      </c>
+      <c r="BI40">
+        <v>0.280101102857859</v>
+      </c>
+    </row>
+    <row r="41" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" t="s">
+        <v>23</v>
+      </c>
+      <c r="O41" t="s">
+        <v>23</v>
+      </c>
+      <c r="P41" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>23</v>
+      </c>
+      <c r="R41" t="s">
+        <v>23</v>
+      </c>
+      <c r="S41" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" t="s">
+        <v>23</v>
+      </c>
+      <c r="U41" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" t="s">
+        <v>23</v>
+      </c>
+      <c r="W41" t="s">
+        <v>23</v>
+      </c>
+      <c r="X41" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL41">
+        <v>0.61498378111102103</v>
+      </c>
+      <c r="AM41">
+        <v>0.69051597014876298</v>
+      </c>
+      <c r="AN41">
+        <v>0.66570889146460799</v>
+      </c>
+      <c r="AO41">
+        <v>0.64877450556585603</v>
+      </c>
+      <c r="AP41">
+        <v>0.68840917732593399</v>
+      </c>
+      <c r="AQ41">
+        <v>0.61274031466840395</v>
+      </c>
+      <c r="AR41">
+        <v>0.69441759718489005</v>
+      </c>
+      <c r="AS41">
+        <v>0.58319832770909097</v>
+      </c>
+      <c r="AT41">
+        <v>0.57230389177003405</v>
+      </c>
+      <c r="AU41">
+        <v>0.56192036134261802</v>
+      </c>
+      <c r="AV41">
+        <v>0.49889625416741301</v>
+      </c>
+      <c r="AW41">
+        <v>0.59554988633357697</v>
+      </c>
+      <c r="AX41">
+        <v>0.69528405035165097</v>
+      </c>
+      <c r="AY41">
+        <v>0.68923925722795099</v>
+      </c>
+      <c r="AZ41">
+        <v>0.16279795689075</v>
+      </c>
+      <c r="BA41">
+        <v>0.15892154694220301</v>
+      </c>
+      <c r="BB41">
+        <v>0.58145311999426197</v>
+      </c>
+      <c r="BC41">
+        <v>0.580153795186375</v>
+      </c>
+      <c r="BD41">
+        <v>0.57628430020690202</v>
+      </c>
+      <c r="BE41">
+        <v>0.31546932323272497</v>
+      </c>
+      <c r="BF41">
+        <v>0.68901331927172504</v>
+      </c>
+      <c r="BG41">
+        <v>0.52994193201316697</v>
+      </c>
+      <c r="BH41">
+        <v>0.53090722481054498</v>
+      </c>
+      <c r="BI41">
+        <v>0.49699081974264497</v>
+      </c>
+    </row>
+    <row r="42" spans="2:61" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" t="s">
+        <v>23</v>
+      </c>
+      <c r="P42" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" t="s">
+        <v>23</v>
+      </c>
+      <c r="S42" t="s">
+        <v>23</v>
+      </c>
+      <c r="T42" t="s">
+        <v>23</v>
+      </c>
+      <c r="U42" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" t="s">
+        <v>23</v>
+      </c>
+      <c r="W42" t="s">
+        <v>23</v>
+      </c>
+      <c r="X42" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B3:BI42">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304A4B3E-6362-4E37-A486-6E35FDEFCC5D}">
   <dimension ref="A1:BI290"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -55711,7 +62934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3116DE92-0BF8-40CB-9782-CBE2ED39D14E}">
   <dimension ref="C3:CX102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -85918,12 +93141,6 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:CX102">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="NaN">
-      <formula>NOT(ISERROR(SEARCH("NaN",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Inf">
-      <formula>NOT(ISERROR(SEARCH("Inf",C3)))</formula>
-    </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -85932,6 +93149,12 @@
         <color theme="5" tint="0.39997558519241921"/>
       </colorScale>
     </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Inf">
+      <formula>NOT(ISERROR(SEARCH("Inf",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="NaN">
+      <formula>NOT(ISERROR(SEARCH("NaN",C3)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
